--- a/jogos_2025-04-16.xlsx
+++ b/jogos_2025-04-16.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="260">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -295,15 +241,15 @@
     <t>Norway Toppserien</t>
   </si>
   <si>
+    <t>Spain Segunda División RFEF Group 1</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Spain Segunda División RFEF Group 1</t>
-  </si>
-  <si>
     <t>England Premier League</t>
   </si>
   <si>
@@ -331,24 +277,24 @@
     <t>2024</t>
   </si>
   <si>
+    <t>Vissel Kobe</t>
+  </si>
+  <si>
     <t>Yokohama F. Marinos</t>
   </si>
   <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
-    <t>Vissel Kobe</t>
-  </si>
-  <si>
     <t>Urawa Reds</t>
   </si>
   <si>
+    <t>Zhejiang FC</t>
+  </si>
+  <si>
     <t>Dalian Zhixing</t>
   </si>
   <si>
-    <t>Zhejiang FC</t>
-  </si>
-  <si>
     <t>Chengdu Better City FC</t>
   </si>
   <si>
@@ -370,66 +316,66 @@
     <t>Kairat</t>
   </si>
   <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
     <t>Gol Gohar</t>
   </si>
   <si>
-    <t>Sparta Praha II</t>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
+    <t>Varnsdorf</t>
+  </si>
+  <si>
+    <t>Slavia Praha U21</t>
   </si>
   <si>
     <t>Bahla</t>
   </si>
   <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
     <t>Baník Ostrava U21</t>
   </si>
   <si>
-    <t>Slavia Praha U21</t>
-  </si>
-  <si>
-    <t>Varnsdorf</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
     <t>Nafta</t>
   </si>
   <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Kolbotn</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
     <t>Bodø / Glimt W</t>
   </si>
   <si>
-    <t>Kolbotn</t>
-  </si>
-  <si>
     <t>Lyn W</t>
   </si>
   <si>
     <t>Trondheims-Ørn</t>
   </si>
   <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
     <t>Al Seeb</t>
   </si>
   <si>
+    <t>Real Avilés</t>
+  </si>
+  <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
     <t>Barcelona W</t>
   </si>
   <si>
-    <t>Silkeborg</t>
-  </si>
-  <si>
-    <t>Real Avilés</t>
-  </si>
-  <si>
     <t>Newcastle United</t>
   </si>
   <si>
@@ -451,37 +397,40 @@
     <t>Botafogo</t>
   </si>
   <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>Mirassol</t>
+    <t>Corinthians</t>
   </si>
   <si>
     <t>Internacional</t>
   </si>
   <si>
-    <t>Corinthians</t>
+    <t>Avaí</t>
   </si>
   <si>
     <t>Paysandu</t>
   </si>
   <si>
-    <t>Avaí</t>
-  </si>
-  <si>
     <t>Atlético Tembetary</t>
   </si>
   <si>
     <t>Coritiba</t>
   </si>
   <si>
+    <t>Flamengo</t>
+  </si>
+  <si>
     <t>Vitória</t>
   </si>
   <si>
     <t>Santos</t>
   </si>
   <si>
-    <t>Flamengo</t>
+    <t>Kawasaki Frontale</t>
   </si>
   <si>
     <t>Shimizu S-Pulse</t>
@@ -490,18 +439,15 @@
     <t>Shanghai SIPG</t>
   </si>
   <si>
-    <t>Kawasaki Frontale</t>
-  </si>
-  <si>
     <t>Kyoto Sanga</t>
   </si>
   <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
     <t>Henan Jianye</t>
   </si>
   <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
     <t>Yunnan Yukun</t>
   </si>
   <si>
@@ -523,66 +469,66 @@
     <t>Atyrau</t>
   </si>
   <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
     <t>Esteghlal</t>
   </si>
   <si>
-    <t>Líšeň</t>
+    <t>Vyškov</t>
+  </si>
+  <si>
+    <t>Sigma Olomouc II</t>
+  </si>
+  <si>
+    <t>Zlín</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
   </si>
   <si>
     <t>Oman Club</t>
   </si>
   <si>
-    <t>Sigma Olomouc II</t>
-  </si>
-  <si>
-    <t>Zlín</t>
-  </si>
-  <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Vyškov</t>
-  </si>
-  <si>
     <t>Maribor</t>
   </si>
   <si>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
     <t>Lillestrøm W</t>
   </si>
   <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
     <t>Stabæk Women</t>
   </si>
   <si>
     <t>Vålerenga Women</t>
   </si>
   <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Brann W</t>
-  </si>
-  <si>
     <t>Al-Nahda</t>
   </si>
   <si>
+    <t>Langreo</t>
+  </si>
+  <si>
+    <t>AaB</t>
+  </si>
+  <si>
     <t>Sevilla W</t>
   </si>
   <si>
-    <t>AaB</t>
-  </si>
-  <si>
-    <t>Langreo</t>
-  </si>
-  <si>
     <t>Crystal Palace</t>
   </si>
   <si>
@@ -604,63 +550,63 @@
     <t>São Paulo</t>
   </si>
   <si>
+    <t>Grêmio</t>
+  </si>
+  <si>
     <t>Bragantino</t>
   </si>
   <si>
-    <t>Grêmio</t>
+    <t>Fluminense</t>
   </si>
   <si>
     <t>Palmeiras</t>
   </si>
   <si>
-    <t>Fluminense</t>
+    <t>Operário PR</t>
   </si>
   <si>
     <t>Chapecoense</t>
   </si>
   <si>
-    <t>Operário PR</t>
-  </si>
-  <si>
     <t>Olimpia</t>
   </si>
   <si>
     <t>Novorizontino</t>
   </si>
   <si>
+    <t>Juventude</t>
+  </si>
+  <si>
     <t>Fortaleza</t>
   </si>
   <si>
     <t>Atlético Mineiro</t>
   </si>
   <si>
-    <t>Juventude</t>
-  </si>
-  <si>
     <t>complete</t>
   </si>
   <si>
     <t>incomplete</t>
   </si>
   <si>
+    <t>['31', '45']</t>
+  </si>
+  <si>
     <t>['29', '51']</t>
   </si>
   <si>
     <t>['83']</t>
   </si>
   <si>
-    <t>['31', '45']</t>
-  </si>
-  <si>
     <t>['24', '61']</t>
   </si>
   <si>
+    <t>['17', '23']</t>
+  </si>
+  <si>
     <t>['69']</t>
   </si>
   <si>
-    <t>['17', '23']</t>
-  </si>
-  <si>
     <t>['42']</t>
   </si>
   <si>
@@ -682,51 +628,51 @@
     <t>['-1']</t>
   </si>
   <si>
+    <t>['5', '48', '83']</t>
+  </si>
+  <si>
     <t>['54', '72']</t>
   </si>
   <si>
     <t>['65']</t>
   </si>
   <si>
+    <t>['59']</t>
+  </si>
+  <si>
+    <t>['71']</t>
+  </si>
+  <si>
     <t>['8', '58', '75']</t>
   </si>
   <si>
-    <t>['71']</t>
-  </si>
-  <si>
-    <t>['59']</t>
-  </si>
-  <si>
-    <t>['5', '48', '83']</t>
-  </si>
-  <si>
     <t>['90']</t>
   </si>
   <si>
+    <t>['43', '48']</t>
+  </si>
+  <si>
     <t>['4', '32', '85']</t>
   </si>
   <si>
+    <t>['8']</t>
+  </si>
+  <si>
     <t>['12', '14', '18', '22', '61', '74']</t>
   </si>
   <si>
     <t>['28', '49']</t>
   </si>
   <si>
-    <t>['8']</t>
-  </si>
-  <si>
-    <t>['43', '48']</t>
-  </si>
-  <si>
     <t>['13', '58']</t>
   </si>
   <si>
+    <t>['8', '14', '22', '33']</t>
+  </si>
+  <si>
     <t>['25', '34', '52', '56', '88']</t>
   </si>
   <si>
-    <t>['8', '14', '22', '33']</t>
-  </si>
-  <si>
     <t>['14', '38', '45+2', '45+8', '58']</t>
   </si>
   <si>
@@ -745,13 +691,16 @@
     <t>['3', '21', '78', '85']</t>
   </si>
   <si>
+    <t>['13', '18', '22', '56', '71', '81']</t>
+  </si>
+  <si>
     <t>['37', '74']</t>
   </si>
   <si>
     <t>['24', '27']</t>
   </si>
   <si>
-    <t>['13', '18', '22', '56', '71', '81']</t>
+    <t>['45+3']</t>
   </si>
   <si>
     <t>['54', '70', '82']</t>
@@ -760,9 +709,6 @@
     <t>['16', '39', '43', '62']</t>
   </si>
   <si>
-    <t>['45+3']</t>
-  </si>
-  <si>
     <t>['55']</t>
   </si>
   <si>
@@ -784,33 +730,33 @@
     <t>['72']</t>
   </si>
   <si>
+    <t>['58']</t>
+  </si>
+  <si>
+    <t>['9']</t>
+  </si>
+  <si>
+    <t>['16', '52']</t>
+  </si>
+  <si>
     <t>['66']</t>
   </si>
   <si>
-    <t>['58']</t>
-  </si>
-  <si>
-    <t>['9']</t>
-  </si>
-  <si>
     <t>['11', '23', '32', '55']</t>
   </si>
   <si>
-    <t>['16', '52']</t>
+    <t>['16', '26', '45', '61', '81']</t>
+  </si>
+  <si>
+    <t>['75']</t>
+  </si>
+  <si>
+    <t>['61']</t>
   </si>
   <si>
     <t>['27', '38', '66', '90']</t>
   </si>
   <si>
-    <t>['75']</t>
-  </si>
-  <si>
-    <t>['61']</t>
-  </si>
-  <si>
-    <t>['16', '26', '45', '61', '81']</t>
-  </si>
-  <si>
     <t>['45+2']</t>
   </si>
   <si>
@@ -832,16 +778,16 @@
     <t>['21', '45+13']</t>
   </si>
   <si>
+    <t>['82']</t>
+  </si>
+  <si>
     <t>['13']</t>
   </si>
   <si>
-    <t>['82']</t>
+    <t>['63', '82']</t>
   </si>
   <si>
     <t>['64']</t>
-  </si>
-  <si>
-    <t>['63', '82']</t>
   </si>
   <si>
     <t>['26', '35']</t>
@@ -1211,10 +1157,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD52"/>
+  <dimension ref="A1:AL52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1329,124 +1275,70 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45763</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="F2" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>189</v>
+      </c>
+      <c r="L2">
+        <v>2.26</v>
+      </c>
+      <c r="M2">
+        <v>3.27</v>
+      </c>
+      <c r="N2">
+        <v>3.11</v>
+      </c>
+      <c r="O2">
+        <v>1.73</v>
+      </c>
+      <c r="P2">
+        <v>8.5</v>
+      </c>
+      <c r="Q2">
+        <v>2.3</v>
+      </c>
+      <c r="R2">
+        <v>1.4</v>
+      </c>
+      <c r="S2">
+        <v>2.75</v>
+      </c>
+      <c r="T2">
         <v>3</v>
       </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
-        <v>207</v>
-      </c>
-      <c r="L2">
-        <v>2.49</v>
-      </c>
-      <c r="M2">
-        <v>3.21</v>
-      </c>
-      <c r="N2">
-        <v>2.8</v>
-      </c>
-      <c r="O2">
-        <v>1.83</v>
-      </c>
-      <c r="P2">
-        <v>8</v>
-      </c>
-      <c r="Q2">
-        <v>2.2</v>
-      </c>
-      <c r="R2">
-        <v>1.44</v>
-      </c>
-      <c r="S2">
-        <v>2.63</v>
-      </c>
-      <c r="T2">
-        <v>3.25</v>
-      </c>
       <c r="U2">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V2">
         <v>9</v>
@@ -1455,463 +1347,301 @@
         <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Z2">
         <v>1.33</v>
       </c>
       <c r="AA2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB2">
+        <v>1.95</v>
+      </c>
+      <c r="AC2">
+        <v>1.79</v>
+      </c>
+      <c r="AD2">
+        <v>3.45</v>
+      </c>
+      <c r="AE2">
+        <v>1.3</v>
+      </c>
+      <c r="AF2">
+        <v>1.75</v>
+      </c>
+      <c r="AG2">
         <v>2</v>
       </c>
-      <c r="AC2">
-        <v>1.75</v>
-      </c>
-      <c r="AD2">
-        <v>3.55</v>
-      </c>
-      <c r="AE2">
-        <v>1.28</v>
-      </c>
-      <c r="AF2">
-        <v>1.8</v>
-      </c>
-      <c r="AG2">
-        <v>1.95</v>
-      </c>
       <c r="AH2">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AI2">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AJ2" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="AK2" t="s">
-        <v>246</v>
-      </c>
-      <c r="AL2">
-        <v>1.42</v>
-      </c>
-      <c r="AM2">
-        <v>1.28</v>
-      </c>
-      <c r="AN2">
-        <v>1.5</v>
-      </c>
-      <c r="AO2">
-        <v>9</v>
-      </c>
-      <c r="AP2">
-        <v>1.32</v>
-      </c>
-      <c r="AQ2">
-        <v>1.56</v>
-      </c>
-      <c r="AR2">
-        <v>1.92</v>
-      </c>
-      <c r="AS2">
-        <v>2.45</v>
-      </c>
-      <c r="AT2">
-        <v>3.15</v>
-      </c>
-      <c r="AU2">
-        <v>2.9</v>
-      </c>
-      <c r="AV2">
-        <v>2.18</v>
-      </c>
-      <c r="AW2">
-        <v>1.73</v>
-      </c>
-      <c r="AX2">
-        <v>1.45</v>
-      </c>
-      <c r="AY2">
-        <v>1.27</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.83</v>
-      </c>
-      <c r="BC2">
-        <v>2.2</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>228</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45763.29166666666</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45763</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" t="s">
         <v>84</v>
       </c>
-      <c r="D3" t="s">
-        <v>102</v>
-      </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="F3" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
       <c r="J3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L3">
-        <v>5.4</v>
+        <v>2.49</v>
       </c>
       <c r="M3">
-        <v>4.8</v>
+        <v>3.21</v>
       </c>
       <c r="N3">
-        <v>1.48</v>
+        <v>2.8</v>
       </c>
       <c r="O3">
-        <v>2.46</v>
+        <v>1.83</v>
       </c>
       <c r="P3">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="Q3">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="R3">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="S3">
-        <v>3.88</v>
+        <v>2.63</v>
       </c>
       <c r="T3">
-        <v>2.13</v>
+        <v>3.25</v>
       </c>
       <c r="U3">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="V3">
-        <v>4.6</v>
+        <v>9</v>
       </c>
       <c r="W3">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y3">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Z3">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AA3">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="AB3">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AC3">
-        <v>2.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD3">
-        <v>2</v>
+        <v>3.55</v>
       </c>
       <c r="AE3">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="AF3">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>2.57</v>
+        <v>1.95</v>
       </c>
       <c r="AH3">
-        <v>3.44</v>
+        <v>7</v>
       </c>
       <c r="AI3">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AJ3" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="AK3" t="s">
-        <v>247</v>
-      </c>
-      <c r="AL3">
-        <v>2.08</v>
-      </c>
-      <c r="AM3">
-        <v>1.22</v>
-      </c>
-      <c r="AN3">
-        <v>1.22</v>
-      </c>
-      <c r="AO3">
-        <v>5</v>
-      </c>
-      <c r="AP3">
-        <v>1.18</v>
-      </c>
-      <c r="AQ3">
-        <v>1.32</v>
-      </c>
-      <c r="AR3">
-        <v>1.52</v>
-      </c>
-      <c r="AS3">
-        <v>1.84</v>
-      </c>
-      <c r="AT3">
-        <v>2.28</v>
-      </c>
-      <c r="AU3">
-        <v>4.1</v>
-      </c>
-      <c r="AV3">
-        <v>3.05</v>
-      </c>
-      <c r="AW3">
-        <v>2.32</v>
-      </c>
-      <c r="AX3">
-        <v>1.84</v>
-      </c>
-      <c r="AY3">
-        <v>1.55</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>2.46</v>
-      </c>
-      <c r="BC3">
-        <v>1.53</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>229</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45763.29166666666</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45763</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="F4" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4" t="s">
+        <v>189</v>
+      </c>
+      <c r="L4">
+        <v>5.4</v>
+      </c>
+      <c r="M4">
+        <v>4.8</v>
+      </c>
+      <c r="N4">
+        <v>1.48</v>
+      </c>
+      <c r="O4">
+        <v>2.46</v>
+      </c>
+      <c r="P4">
+        <v>22</v>
+      </c>
+      <c r="Q4">
+        <v>1.53</v>
+      </c>
+      <c r="R4">
+        <v>1.2</v>
+      </c>
+      <c r="S4">
+        <v>3.88</v>
+      </c>
+      <c r="T4">
+        <v>2.13</v>
+      </c>
+      <c r="U4">
+        <v>1.67</v>
+      </c>
+      <c r="V4">
+        <v>4.6</v>
+      </c>
+      <c r="W4">
+        <v>1.14</v>
+      </c>
+      <c r="X4">
+        <v>1.01</v>
+      </c>
+      <c r="Y4">
+        <v>17</v>
+      </c>
+      <c r="Z4">
+        <v>1.08</v>
+      </c>
+      <c r="AA4">
+        <v>5.6</v>
+      </c>
+      <c r="AB4">
+        <v>1.4</v>
+      </c>
+      <c r="AC4">
+        <v>2.73</v>
+      </c>
+      <c r="AD4">
         <v>2</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>207</v>
-      </c>
-      <c r="L4">
-        <v>2.26</v>
-      </c>
-      <c r="M4">
-        <v>3.27</v>
-      </c>
-      <c r="N4">
-        <v>3.11</v>
-      </c>
-      <c r="O4">
-        <v>1.73</v>
-      </c>
-      <c r="P4">
-        <v>8.5</v>
-      </c>
-      <c r="Q4">
-        <v>2.3</v>
-      </c>
-      <c r="R4">
-        <v>1.4</v>
-      </c>
-      <c r="S4">
-        <v>2.75</v>
-      </c>
-      <c r="T4">
-        <v>3</v>
-      </c>
-      <c r="U4">
-        <v>1.36</v>
-      </c>
-      <c r="V4">
-        <v>9</v>
-      </c>
-      <c r="W4">
-        <v>1.07</v>
-      </c>
-      <c r="X4">
-        <v>1.06</v>
-      </c>
-      <c r="Y4">
-        <v>8.5</v>
-      </c>
-      <c r="Z4">
-        <v>1.33</v>
-      </c>
-      <c r="AA4">
-        <v>3.25</v>
-      </c>
-      <c r="AB4">
-        <v>1.95</v>
-      </c>
-      <c r="AC4">
-        <v>1.79</v>
-      </c>
-      <c r="AD4">
-        <v>3.45</v>
-      </c>
       <c r="AE4">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AF4">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>2.57</v>
       </c>
       <c r="AH4">
-        <v>6.5</v>
+        <v>3.44</v>
       </c>
       <c r="AI4">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AJ4" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="AK4" t="s">
-        <v>248</v>
-      </c>
-      <c r="AL4">
-        <v>1.35</v>
-      </c>
-      <c r="AM4">
-        <v>1.28</v>
-      </c>
-      <c r="AN4">
-        <v>1.6</v>
-      </c>
-      <c r="AO4">
-        <v>9</v>
-      </c>
-      <c r="AP4">
-        <v>1.29</v>
-      </c>
-      <c r="AQ4">
-        <v>1.5</v>
-      </c>
-      <c r="AR4">
-        <v>1.83</v>
-      </c>
-      <c r="AS4">
-        <v>2.32</v>
-      </c>
-      <c r="AT4">
-        <v>2.95</v>
-      </c>
-      <c r="AU4">
-        <v>3.1</v>
-      </c>
-      <c r="AV4">
-        <v>2.32</v>
-      </c>
-      <c r="AW4">
-        <v>1.81</v>
-      </c>
-      <c r="AX4">
-        <v>1.5</v>
-      </c>
-      <c r="AY4">
-        <v>1.3</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>1.73</v>
-      </c>
-      <c r="BC4">
-        <v>2.3</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>230</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45763.29166666666</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45763</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="F5" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1926,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L5">
         <v>2.1</v>
@@ -2001,427 +1731,265 @@
         <v>1.08</v>
       </c>
       <c r="AJ5" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="AK5" t="s">
-        <v>249</v>
-      </c>
-      <c r="AL5">
-        <v>1.3</v>
-      </c>
-      <c r="AM5">
-        <v>1.28</v>
-      </c>
-      <c r="AN5">
-        <v>1.65</v>
-      </c>
-      <c r="AO5">
-        <v>9</v>
-      </c>
-      <c r="AP5">
-        <v>1.28</v>
-      </c>
-      <c r="AQ5">
-        <v>1.5</v>
-      </c>
-      <c r="AR5">
-        <v>1.81</v>
-      </c>
-      <c r="AS5">
-        <v>2.28</v>
-      </c>
-      <c r="AT5">
-        <v>2.95</v>
-      </c>
-      <c r="AU5">
-        <v>3.15</v>
-      </c>
-      <c r="AV5">
-        <v>2.32</v>
-      </c>
-      <c r="AW5">
-        <v>1.83</v>
-      </c>
-      <c r="AX5">
-        <v>1.52</v>
-      </c>
-      <c r="AY5">
-        <v>1.32</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>1.83</v>
-      </c>
-      <c r="BC5">
-        <v>2.35</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>231</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45763.3125</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45763</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" t="s">
         <v>84</v>
       </c>
-      <c r="D6" t="s">
-        <v>102</v>
-      </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F6" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L6">
-        <v>2.51</v>
+        <v>1.38</v>
       </c>
       <c r="M6">
-        <v>3.31</v>
+        <v>5.2</v>
       </c>
       <c r="N6">
-        <v>2.74</v>
+        <v>6.6</v>
       </c>
       <c r="O6">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="P6">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="Q6">
-        <v>2.02</v>
+        <v>3</v>
       </c>
       <c r="R6">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="S6">
-        <v>2.94</v>
+        <v>3.8</v>
       </c>
       <c r="T6">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="U6">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="V6">
-        <v>6.65</v>
+        <v>4.2</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="X6">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Z6">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AA6">
-        <v>3.88</v>
+        <v>5.25</v>
       </c>
       <c r="AB6">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AC6">
-        <v>2.01</v>
+        <v>2.73</v>
       </c>
       <c r="AD6">
-        <v>2.79</v>
+        <v>1.92</v>
       </c>
       <c r="AE6">
-        <v>1.34</v>
+        <v>1.82</v>
       </c>
       <c r="AF6">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AG6">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AH6">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="AI6">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AJ6" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="AK6" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL6">
-        <v>1.42</v>
-      </c>
-      <c r="AM6">
-        <v>1.31</v>
-      </c>
-      <c r="AN6">
-        <v>1.52</v>
-      </c>
-      <c r="AO6">
-        <v>10</v>
-      </c>
-      <c r="AP6">
-        <v>1.27</v>
-      </c>
-      <c r="AQ6">
-        <v>1.47</v>
-      </c>
-      <c r="AR6">
-        <v>1.76</v>
-      </c>
-      <c r="AS6">
-        <v>2.18</v>
-      </c>
-      <c r="AT6">
-        <v>2.8</v>
-      </c>
-      <c r="AU6">
-        <v>3.3</v>
-      </c>
-      <c r="AV6">
-        <v>2.48</v>
-      </c>
-      <c r="AW6">
-        <v>1.94</v>
-      </c>
-      <c r="AX6">
-        <v>1.58</v>
-      </c>
-      <c r="AY6">
-        <v>1.36</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>1.89</v>
-      </c>
-      <c r="BC6">
-        <v>2.02</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>232</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45763.33333333334</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45763</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" t="s">
         <v>84</v>
       </c>
-      <c r="D7" t="s">
-        <v>102</v>
-      </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="F7" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L7">
-        <v>1.38</v>
+        <v>2.51</v>
       </c>
       <c r="M7">
-        <v>5.2</v>
+        <v>3.31</v>
       </c>
       <c r="N7">
-        <v>6.6</v>
+        <v>2.74</v>
       </c>
       <c r="O7">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="P7">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="Q7">
-        <v>3</v>
+        <v>2.02</v>
       </c>
       <c r="R7">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="S7">
-        <v>3.8</v>
+        <v>2.94</v>
       </c>
       <c r="T7">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="U7">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="V7">
-        <v>4.2</v>
+        <v>6.65</v>
       </c>
       <c r="W7">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Z7">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AA7">
-        <v>5.25</v>
+        <v>3.88</v>
       </c>
       <c r="AB7">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AC7">
-        <v>2.73</v>
+        <v>2.01</v>
       </c>
       <c r="AD7">
-        <v>1.92</v>
+        <v>2.79</v>
       </c>
       <c r="AE7">
-        <v>1.82</v>
+        <v>1.34</v>
       </c>
       <c r="AF7">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AG7">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AH7">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="AI7">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AJ7" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="AK7" t="s">
-        <v>250</v>
-      </c>
-      <c r="AL7">
-        <v>1.07</v>
-      </c>
-      <c r="AM7">
-        <v>1.13</v>
-      </c>
-      <c r="AN7">
-        <v>2.75</v>
-      </c>
-      <c r="AO7">
-        <v>8</v>
-      </c>
-      <c r="AP7">
-        <v>1.25</v>
-      </c>
-      <c r="AQ7">
-        <v>1.44</v>
-      </c>
-      <c r="AR7">
-        <v>1.72</v>
-      </c>
-      <c r="AS7">
-        <v>2.12</v>
-      </c>
-      <c r="AT7">
-        <v>2.7</v>
-      </c>
-      <c r="AU7">
-        <v>3.4</v>
-      </c>
-      <c r="AV7">
-        <v>2.55</v>
-      </c>
-      <c r="AW7">
-        <v>1.98</v>
-      </c>
-      <c r="AX7">
-        <v>1.62</v>
-      </c>
-      <c r="AY7">
-        <v>1.4</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>1.4</v>
-      </c>
-      <c r="BC7">
-        <v>3</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45763.33333333334</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45763</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" t="s">
         <v>84</v>
       </c>
-      <c r="D8" t="s">
-        <v>102</v>
-      </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="F8" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -2436,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L8">
         <v>1.36</v>
@@ -2511,87 +2079,33 @@
         <v>1.23</v>
       </c>
       <c r="AJ8" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="AK8" t="s">
-        <v>251</v>
-      </c>
-      <c r="AL8">
-        <v>1.05</v>
-      </c>
-      <c r="AM8">
-        <v>1.14</v>
-      </c>
-      <c r="AN8">
-        <v>3.4</v>
-      </c>
-      <c r="AO8">
-        <v>6</v>
-      </c>
-      <c r="AP8">
-        <v>1.32</v>
-      </c>
-      <c r="AQ8">
-        <v>1.54</v>
-      </c>
-      <c r="AR8">
-        <v>1.88</v>
-      </c>
-      <c r="AS8">
-        <v>2.32</v>
-      </c>
-      <c r="AT8">
-        <v>2.9</v>
-      </c>
-      <c r="AU8">
-        <v>3.05</v>
-      </c>
-      <c r="AV8">
-        <v>2.3</v>
-      </c>
-      <c r="AW8">
-        <v>1.81</v>
-      </c>
-      <c r="AX8">
-        <v>1.53</v>
-      </c>
-      <c r="AY8">
-        <v>1.34</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>1.28</v>
-      </c>
-      <c r="BC8">
-        <v>3.68</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>233</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45763.35763888889</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45763</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" t="s">
         <v>85</v>
       </c>
-      <c r="D9" t="s">
-        <v>103</v>
-      </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="F9" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -2606,7 +2120,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L9">
         <v>34</v>
@@ -2681,87 +2195,33 @@
         <v>1.16</v>
       </c>
       <c r="AJ9" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="AK9" t="s">
-        <v>252</v>
-      </c>
-      <c r="AL9">
-        <v>2.58</v>
-      </c>
-      <c r="AM9">
-        <v>1.19</v>
-      </c>
-      <c r="AN9">
-        <v>1.1</v>
-      </c>
-      <c r="AO9">
-        <v>3</v>
-      </c>
-      <c r="AP9">
-        <v>1.35</v>
-      </c>
-      <c r="AQ9">
-        <v>1.67</v>
-      </c>
-      <c r="AR9">
-        <v>2.08</v>
-      </c>
-      <c r="AS9">
-        <v>2.78</v>
-      </c>
-      <c r="AT9">
-        <v>3.88</v>
-      </c>
-      <c r="AU9">
-        <v>2.84</v>
-      </c>
-      <c r="AV9">
-        <v>2.14</v>
-      </c>
-      <c r="AW9">
-        <v>1.71</v>
-      </c>
-      <c r="AX9">
-        <v>1.36</v>
-      </c>
-      <c r="AY9">
-        <v>1.2</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>3.2</v>
-      </c>
-      <c r="BC9">
-        <v>1.39</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>234</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45763.36458333334</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45763</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s">
         <v>84</v>
       </c>
-      <c r="D10" t="s">
-        <v>102</v>
-      </c>
       <c r="E10" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="F10" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="G10">
         <v>3</v>
@@ -2776,7 +2236,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L10">
         <v>1.15</v>
@@ -2851,87 +2311,33 @@
         <v>1.27</v>
       </c>
       <c r="AJ10" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="AK10" t="s">
-        <v>253</v>
-      </c>
-      <c r="AL10">
-        <v>1.01</v>
-      </c>
-      <c r="AM10">
-        <v>1.06</v>
-      </c>
-      <c r="AN10">
-        <v>5.65</v>
-      </c>
-      <c r="AO10">
-        <v>16</v>
-      </c>
-      <c r="AP10">
-        <v>1.2</v>
-      </c>
-      <c r="AQ10">
-        <v>1.36</v>
-      </c>
-      <c r="AR10">
-        <v>1.58</v>
-      </c>
-      <c r="AS10">
-        <v>1.91</v>
-      </c>
-      <c r="AT10">
-        <v>2.38</v>
-      </c>
-      <c r="AU10">
-        <v>3.9</v>
-      </c>
-      <c r="AV10">
-        <v>2.85</v>
-      </c>
-      <c r="AW10">
-        <v>2.18</v>
-      </c>
-      <c r="AX10">
-        <v>1.78</v>
-      </c>
-      <c r="AY10">
-        <v>1.5</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>1.14</v>
-      </c>
-      <c r="BC10">
-        <v>5.35</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>235</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45763.375</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45763</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
         <v>86</v>
       </c>
-      <c r="D11" t="s">
-        <v>104</v>
-      </c>
       <c r="E11" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="F11" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2946,7 +2352,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3021,87 +2427,33 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="AK11" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>0</v>
-      </c>
-      <c r="AO11">
-        <v>-1</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
-      <c r="AR11">
-        <v>0</v>
-      </c>
-      <c r="AS11">
-        <v>0</v>
-      </c>
-      <c r="AT11">
-        <v>0</v>
-      </c>
-      <c r="AU11">
-        <v>0</v>
-      </c>
-      <c r="AV11">
-        <v>0</v>
-      </c>
-      <c r="AW11">
-        <v>0</v>
-      </c>
-      <c r="AX11">
-        <v>0</v>
-      </c>
-      <c r="AY11">
-        <v>0</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>0</v>
-      </c>
-      <c r="BC11">
-        <v>0</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45763.38541666666</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45763</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="F12" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -3116,7 +2468,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L12">
         <v>2.65</v>
@@ -3191,87 +2543,33 @@
         <v>1.02</v>
       </c>
       <c r="AJ12" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="AK12" t="s">
-        <v>254</v>
-      </c>
-      <c r="AL12">
-        <v>1.35</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>1.35</v>
-      </c>
-      <c r="AO12">
-        <v>5</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>1.91</v>
-      </c>
-      <c r="BC12">
-        <v>2.4</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>236</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45763.4375</v>
       </c>
     </row>
-    <row r="13" spans="1:56">
+    <row r="13" spans="1:38">
       <c r="A13" s="2">
         <v>45763</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E13" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="F13" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="G13">
         <v>3</v>
@@ -3286,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L13">
         <v>2.02</v>
@@ -3361,87 +2659,33 @@
         <v>1.03</v>
       </c>
       <c r="AJ13" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="AK13" t="s">
-        <v>255</v>
-      </c>
-      <c r="AL13">
-        <v>1.3</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>1.75</v>
-      </c>
-      <c r="AO13">
-        <v>4</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13">
-        <v>0</v>
-      </c>
-      <c r="AV13">
-        <v>0</v>
-      </c>
-      <c r="AW13">
-        <v>0</v>
-      </c>
-      <c r="AX13">
-        <v>0</v>
-      </c>
-      <c r="AY13">
-        <v>0</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.83</v>
-      </c>
-      <c r="BC13">
-        <v>2.5</v>
-      </c>
-      <c r="BD13" s="3">
+        <v>237</v>
+      </c>
+      <c r="AL13" s="3">
         <v>45763.45138888889</v>
       </c>
     </row>
-    <row r="14" spans="1:56">
+    <row r="14" spans="1:38">
       <c r="A14" s="2">
         <v>45763</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E14" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="F14" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="G14">
         <v>4</v>
@@ -3456,7 +2700,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L14">
         <v>1.25</v>
@@ -3531,93 +2775,39 @@
         <v>1.11</v>
       </c>
       <c r="AJ14" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="AK14" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL14">
-        <v>1.04</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>3.88</v>
-      </c>
-      <c r="AO14">
-        <v>12</v>
-      </c>
-      <c r="AP14">
-        <v>1.51</v>
-      </c>
-      <c r="AQ14">
-        <v>1.88</v>
-      </c>
-      <c r="AR14">
-        <v>2.85</v>
-      </c>
-      <c r="AS14">
-        <v>3.2</v>
-      </c>
-      <c r="AT14">
-        <v>4.3</v>
-      </c>
-      <c r="AU14">
-        <v>2.38</v>
-      </c>
-      <c r="AV14">
-        <v>1.86</v>
-      </c>
-      <c r="AW14">
-        <v>1.53</v>
-      </c>
-      <c r="AX14">
-        <v>1.3</v>
-      </c>
-      <c r="AY14">
-        <v>1.16</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>1.17</v>
-      </c>
-      <c r="BC14">
-        <v>5.5</v>
-      </c>
-      <c r="BD14" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL14" s="3">
         <v>45763.45833333334</v>
       </c>
     </row>
-    <row r="15" spans="1:56">
+    <row r="15" spans="1:38">
       <c r="A15" s="2">
         <v>45763</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E15" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="F15" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -3626,168 +2816,114 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L15">
+        <v>2.05</v>
+      </c>
+      <c r="M15">
+        <v>3.31</v>
+      </c>
+      <c r="N15">
+        <v>3.08</v>
+      </c>
+      <c r="O15">
+        <v>1.67</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
         <v>2.4</v>
       </c>
-      <c r="M15">
-        <v>2.7</v>
-      </c>
-      <c r="N15">
+      <c r="R15">
+        <v>1.36</v>
+      </c>
+      <c r="S15">
+        <v>2.88</v>
+      </c>
+      <c r="T15">
+        <v>2.62</v>
+      </c>
+      <c r="U15">
+        <v>1.44</v>
+      </c>
+      <c r="V15">
+        <v>6.8</v>
+      </c>
+      <c r="W15">
+        <v>1.07</v>
+      </c>
+      <c r="X15">
+        <v>1.01</v>
+      </c>
+      <c r="Y15">
+        <v>10</v>
+      </c>
+      <c r="Z15">
+        <v>1.29</v>
+      </c>
+      <c r="AA15">
+        <v>3.4</v>
+      </c>
+      <c r="AB15">
+        <v>1.9</v>
+      </c>
+      <c r="AC15">
+        <v>1.85</v>
+      </c>
+      <c r="AD15">
         <v>3</v>
       </c>
-      <c r="O15">
-        <v>2.5</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
+      <c r="AE15">
+        <v>1.33</v>
+      </c>
+      <c r="AF15">
+        <v>1.67</v>
+      </c>
+      <c r="AG15">
         <v>2</v>
       </c>
-      <c r="R15">
-        <v>1.73</v>
-      </c>
-      <c r="S15">
-        <v>2.3</v>
-      </c>
-      <c r="T15">
-        <v>4.5</v>
-      </c>
-      <c r="U15">
-        <v>1.16</v>
-      </c>
-      <c r="V15">
-        <v>9.6</v>
-      </c>
-      <c r="W15">
-        <v>1.01</v>
-      </c>
-      <c r="X15">
-        <v>1.15</v>
-      </c>
-      <c r="Y15">
-        <v>5</v>
-      </c>
-      <c r="Z15">
-        <v>1.66</v>
-      </c>
-      <c r="AA15">
-        <v>2.05</v>
-      </c>
-      <c r="AB15">
-        <v>3</v>
-      </c>
-      <c r="AC15">
-        <v>1.34</v>
-      </c>
-      <c r="AD15">
-        <v>7</v>
-      </c>
-      <c r="AE15">
-        <v>1.09</v>
-      </c>
-      <c r="AF15">
-        <v>2.3</v>
-      </c>
-      <c r="AG15">
-        <v>1.5</v>
-      </c>
       <c r="AH15">
-        <v>14</v>
+        <v>5.85</v>
       </c>
       <c r="AI15">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AJ15" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="AK15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AL15">
-        <v>1.36</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>1.47</v>
-      </c>
-      <c r="AO15">
-        <v>3</v>
-      </c>
-      <c r="AP15">
-        <v>0</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>0</v>
-      </c>
-      <c r="AS15">
-        <v>0</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15">
-        <v>0</v>
-      </c>
-      <c r="AV15">
-        <v>0</v>
-      </c>
-      <c r="AW15">
-        <v>0</v>
-      </c>
-      <c r="AX15">
-        <v>0</v>
-      </c>
-      <c r="AY15">
-        <v>0</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>2.5</v>
-      </c>
-      <c r="BC15">
-        <v>2</v>
-      </c>
-      <c r="BD15" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL15" s="3">
         <v>45763.47916666666</v>
       </c>
     </row>
-    <row r="16" spans="1:56">
+    <row r="16" spans="1:38">
       <c r="A16" s="2">
         <v>45763</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="F16" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -3796,189 +2932,135 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L16">
+        <v>2.4</v>
+      </c>
+      <c r="M16">
+        <v>2.7</v>
+      </c>
+      <c r="N16">
+        <v>3</v>
+      </c>
+      <c r="O16">
+        <v>2.5</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>2</v>
+      </c>
+      <c r="R16">
+        <v>1.73</v>
+      </c>
+      <c r="S16">
+        <v>2.3</v>
+      </c>
+      <c r="T16">
+        <v>4.5</v>
+      </c>
+      <c r="U16">
+        <v>1.16</v>
+      </c>
+      <c r="V16">
+        <v>9.6</v>
+      </c>
+      <c r="W16">
+        <v>1.01</v>
+      </c>
+      <c r="X16">
+        <v>1.15</v>
+      </c>
+      <c r="Y16">
+        <v>5</v>
+      </c>
+      <c r="Z16">
+        <v>1.66</v>
+      </c>
+      <c r="AA16">
         <v>2.05</v>
       </c>
-      <c r="M16">
-        <v>3.31</v>
-      </c>
-      <c r="N16">
-        <v>3.08</v>
-      </c>
-      <c r="O16">
-        <v>1.67</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>2.4</v>
-      </c>
-      <c r="R16">
-        <v>1.36</v>
-      </c>
-      <c r="S16">
-        <v>2.88</v>
-      </c>
-      <c r="T16">
-        <v>2.62</v>
-      </c>
-      <c r="U16">
-        <v>1.44</v>
-      </c>
-      <c r="V16">
-        <v>6.8</v>
-      </c>
-      <c r="W16">
-        <v>1.07</v>
-      </c>
-      <c r="X16">
-        <v>1.01</v>
-      </c>
-      <c r="Y16">
-        <v>10</v>
-      </c>
-      <c r="Z16">
-        <v>1.29</v>
-      </c>
-      <c r="AA16">
-        <v>3.4</v>
-      </c>
       <c r="AB16">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="AC16">
-        <v>1.85</v>
+        <v>1.34</v>
       </c>
       <c r="AD16">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE16">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AF16">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AH16">
-        <v>5.85</v>
+        <v>14</v>
       </c>
       <c r="AI16">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AJ16" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="AK16" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL16">
-        <v>1.3</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>1.47</v>
-      </c>
-      <c r="AO16">
-        <v>12</v>
-      </c>
-      <c r="AP16">
-        <v>1.16</v>
-      </c>
-      <c r="AQ16">
-        <v>1.31</v>
-      </c>
-      <c r="AR16">
-        <v>1.69</v>
-      </c>
-      <c r="AS16">
-        <v>1.89</v>
-      </c>
-      <c r="AT16">
-        <v>2.34</v>
-      </c>
-      <c r="AU16">
-        <v>4.3</v>
-      </c>
-      <c r="AV16">
-        <v>3.05</v>
-      </c>
-      <c r="AW16">
-        <v>2.34</v>
-      </c>
-      <c r="AX16">
-        <v>1.85</v>
-      </c>
-      <c r="AY16">
-        <v>1.54</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>1.67</v>
-      </c>
-      <c r="BC16">
-        <v>2.4</v>
-      </c>
-      <c r="BD16" s="3">
+        <v>203</v>
+      </c>
+      <c r="AL16" s="3">
         <v>45763.47916666666</v>
       </c>
     </row>
-    <row r="17" spans="1:56">
+    <row r="17" spans="1:38">
       <c r="A17" s="2">
         <v>45763</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E17" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F17" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
         <v>1</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L17">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="M17">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N17">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="O17">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -3987,141 +3069,87 @@
         <v>2.2</v>
       </c>
       <c r="R17">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S17">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T17">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U17">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W17">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>6.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z17">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AA17">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AB17">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AC17">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AD17">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AE17">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF17">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG17">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AH17">
-        <v>7</v>
+        <v>9.1</v>
       </c>
       <c r="AI17">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AJ17" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="AK17" t="s">
-        <v>256</v>
-      </c>
-      <c r="AL17">
-        <v>1.3</v>
-      </c>
-      <c r="AM17">
-        <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>1.44</v>
-      </c>
-      <c r="AO17">
-        <v>12</v>
-      </c>
-      <c r="AP17">
-        <v>0</v>
-      </c>
-      <c r="AQ17">
-        <v>1.85</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17">
-        <v>0</v>
-      </c>
-      <c r="AV17">
-        <v>1.85</v>
-      </c>
-      <c r="AW17">
-        <v>0</v>
-      </c>
-      <c r="AX17">
-        <v>0</v>
-      </c>
-      <c r="AY17">
-        <v>0</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>1.95</v>
-      </c>
-      <c r="BC17">
-        <v>2.2</v>
-      </c>
-      <c r="BD17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL17" s="3">
         <v>45763.5</v>
       </c>
     </row>
-    <row r="18" spans="1:56">
+    <row r="18" spans="1:38">
       <c r="A18" s="2">
         <v>45763</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" t="s">
         <v>103</v>
       </c>
-      <c r="E18" t="s">
-        <v>121</v>
-      </c>
       <c r="F18" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -4136,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L18">
         <v>1.87</v>
@@ -4211,87 +3239,33 @@
         <v>1.09</v>
       </c>
       <c r="AJ18" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="AK18" t="s">
-        <v>257</v>
-      </c>
-      <c r="AL18">
-        <v>1.22</v>
-      </c>
-      <c r="AM18">
-        <v>0</v>
-      </c>
-      <c r="AN18">
-        <v>1.7</v>
-      </c>
-      <c r="AO18">
-        <v>8</v>
-      </c>
-      <c r="AP18">
-        <v>1.21</v>
-      </c>
-      <c r="AQ18">
-        <v>1.4</v>
-      </c>
-      <c r="AR18">
-        <v>1.86</v>
-      </c>
-      <c r="AS18">
-        <v>2.07</v>
-      </c>
-      <c r="AT18">
-        <v>2.58</v>
-      </c>
-      <c r="AU18">
-        <v>3.78</v>
-      </c>
-      <c r="AV18">
-        <v>2.72</v>
-      </c>
-      <c r="AW18">
-        <v>2.12</v>
-      </c>
-      <c r="AX18">
-        <v>1.71</v>
-      </c>
-      <c r="AY18">
-        <v>1.44</v>
-      </c>
-      <c r="AZ18">
-        <v>0</v>
-      </c>
-      <c r="BA18">
-        <v>0</v>
-      </c>
-      <c r="BB18">
-        <v>1.67</v>
-      </c>
-      <c r="BC18">
-        <v>2.38</v>
-      </c>
-      <c r="BD18" s="3">
+        <v>238</v>
+      </c>
+      <c r="AL18" s="3">
         <v>45763.5</v>
       </c>
     </row>
-    <row r="19" spans="1:56">
+    <row r="19" spans="1:38">
       <c r="A19" s="2">
         <v>45763</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D19" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="F19" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -4306,7 +3280,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L19">
         <v>3.35</v>
@@ -4381,257 +3355,149 @@
         <v>1.04</v>
       </c>
       <c r="AJ19" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="AK19" t="s">
-        <v>258</v>
-      </c>
-      <c r="AL19">
-        <v>1.3</v>
-      </c>
-      <c r="AM19">
-        <v>0</v>
-      </c>
-      <c r="AN19">
-        <v>1.22</v>
-      </c>
-      <c r="AO19">
-        <v>8</v>
-      </c>
-      <c r="AP19">
-        <v>1.17</v>
-      </c>
-      <c r="AQ19">
-        <v>1.34</v>
-      </c>
-      <c r="AR19">
-        <v>1.63</v>
-      </c>
-      <c r="AS19">
-        <v>2.09</v>
-      </c>
-      <c r="AT19">
-        <v>2.62</v>
-      </c>
-      <c r="AU19">
-        <v>4.05</v>
-      </c>
-      <c r="AV19">
-        <v>2.78</v>
-      </c>
-      <c r="AW19">
-        <v>2.09</v>
-      </c>
-      <c r="AX19">
-        <v>1.69</v>
-      </c>
-      <c r="AY19">
-        <v>1.38</v>
-      </c>
-      <c r="AZ19">
-        <v>0</v>
-      </c>
-      <c r="BA19">
-        <v>0</v>
-      </c>
-      <c r="BB19">
-        <v>2.5</v>
-      </c>
-      <c r="BC19">
-        <v>1.67</v>
-      </c>
-      <c r="BD19" s="3">
+        <v>239</v>
+      </c>
+      <c r="AL19" s="3">
         <v>45763.5</v>
       </c>
     </row>
-    <row r="20" spans="1:56">
+    <row r="20" spans="1:38">
       <c r="A20" s="2">
         <v>45763</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="F20" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
         <v>1</v>
       </c>
-      <c r="J20">
-        <v>3</v>
-      </c>
       <c r="K20" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L20">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="M20">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O20">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="P20">
         <v>0</v>
       </c>
       <c r="Q20">
+        <v>2.1</v>
+      </c>
+      <c r="R20">
+        <v>1.36</v>
+      </c>
+      <c r="S20">
+        <v>2.9</v>
+      </c>
+      <c r="T20">
         <v>2.6</v>
-      </c>
-      <c r="R20">
-        <v>1.38</v>
-      </c>
-      <c r="S20">
-        <v>2.8</v>
-      </c>
-      <c r="T20">
-        <v>2.8</v>
       </c>
       <c r="U20">
         <v>1.4</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="Z20">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AA20">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB20">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AC20">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AD20">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AE20">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AF20">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG20">
         <v>2</v>
       </c>
       <c r="AH20">
-        <v>5.8</v>
+        <v>6.85</v>
       </c>
       <c r="AI20">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AJ20" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="AK20" t="s">
-        <v>259</v>
-      </c>
-      <c r="AL20">
-        <v>1.25</v>
-      </c>
-      <c r="AM20">
-        <v>0</v>
-      </c>
-      <c r="AN20">
-        <v>1.57</v>
-      </c>
-      <c r="AO20">
-        <v>15</v>
-      </c>
-      <c r="AP20">
-        <v>1.14</v>
-      </c>
-      <c r="AQ20">
-        <v>1.22</v>
-      </c>
-      <c r="AR20">
-        <v>1.59</v>
-      </c>
-      <c r="AS20">
-        <v>1.79</v>
-      </c>
-      <c r="AT20">
-        <v>2.19</v>
-      </c>
-      <c r="AU20">
-        <v>4.7</v>
-      </c>
-      <c r="AV20">
-        <v>3.5</v>
-      </c>
-      <c r="AW20">
-        <v>2.48</v>
-      </c>
-      <c r="AX20">
-        <v>2</v>
-      </c>
-      <c r="AY20">
-        <v>1.57</v>
-      </c>
-      <c r="AZ20">
-        <v>0</v>
-      </c>
-      <c r="BA20">
-        <v>0</v>
-      </c>
-      <c r="BB20">
-        <v>1.57</v>
-      </c>
-      <c r="BC20">
-        <v>2.6</v>
-      </c>
-      <c r="BD20" s="3">
+        <v>240</v>
+      </c>
+      <c r="AL20" s="3">
         <v>45763.5</v>
       </c>
     </row>
-    <row r="21" spans="1:56">
+    <row r="21" spans="1:38">
       <c r="A21" s="2">
         <v>45763</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E21" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F21" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -4646,7 +3512,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L21">
         <v>1.7</v>
@@ -4721,427 +3587,265 @@
         <v>1.13</v>
       </c>
       <c r="AJ21" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="AK21" t="s">
-        <v>213</v>
-      </c>
-      <c r="AL21">
-        <v>1.25</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
-      </c>
-      <c r="AN21">
-        <v>2.09</v>
-      </c>
-      <c r="AO21">
-        <v>10</v>
-      </c>
-      <c r="AP21">
-        <v>1.18</v>
-      </c>
-      <c r="AQ21">
-        <v>1.3</v>
-      </c>
-      <c r="AR21">
-        <v>1.76</v>
-      </c>
-      <c r="AS21">
-        <v>1.91</v>
-      </c>
-      <c r="AT21">
-        <v>2.44</v>
-      </c>
-      <c r="AU21">
-        <v>4.05</v>
-      </c>
-      <c r="AV21">
-        <v>2.97</v>
-      </c>
-      <c r="AW21">
-        <v>2.23</v>
-      </c>
-      <c r="AX21">
-        <v>1.8</v>
-      </c>
-      <c r="AY21">
-        <v>1.49</v>
-      </c>
-      <c r="AZ21">
-        <v>0</v>
-      </c>
-      <c r="BA21">
-        <v>0</v>
-      </c>
-      <c r="BB21">
-        <v>1.53</v>
-      </c>
-      <c r="BC21">
-        <v>2.6</v>
-      </c>
-      <c r="BD21" s="3">
+        <v>196</v>
+      </c>
+      <c r="AL21" s="3">
         <v>45763.5</v>
       </c>
     </row>
-    <row r="22" spans="1:56">
+    <row r="22" spans="1:38">
       <c r="A22" s="2">
         <v>45763</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="F22" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
         <v>1</v>
       </c>
-      <c r="H22">
-        <v>2</v>
-      </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L22">
+        <v>2.6</v>
+      </c>
+      <c r="M22">
+        <v>3</v>
+      </c>
+      <c r="N22">
+        <v>2.5</v>
+      </c>
+      <c r="O22">
+        <v>1.95</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
         <v>2.2</v>
       </c>
-      <c r="M22">
-        <v>3.1</v>
-      </c>
-      <c r="N22">
-        <v>3.2</v>
-      </c>
-      <c r="O22">
-        <v>1.8</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>2.1</v>
-      </c>
       <c r="R22">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S22">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="T22">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="U22">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="V22">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y22">
-        <v>10.5</v>
+        <v>6.25</v>
       </c>
       <c r="Z22">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AA22">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB22">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="AC22">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="AD22">
-        <v>3.28</v>
+        <v>4.4</v>
       </c>
       <c r="AE22">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AF22">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AG22">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AH22">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="AI22">
         <v>1.06</v>
       </c>
       <c r="AJ22" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="AK22" t="s">
-        <v>260</v>
-      </c>
-      <c r="AL22">
-        <v>1.33</v>
-      </c>
-      <c r="AM22">
-        <v>0</v>
-      </c>
-      <c r="AN22">
-        <v>1.66</v>
-      </c>
-      <c r="AO22">
-        <v>11</v>
-      </c>
-      <c r="AP22">
-        <v>1.15</v>
-      </c>
-      <c r="AQ22">
-        <v>1.25</v>
-      </c>
-      <c r="AR22">
-        <v>1.48</v>
-      </c>
-      <c r="AS22">
-        <v>1.81</v>
-      </c>
-      <c r="AT22">
-        <v>2.29</v>
-      </c>
-      <c r="AU22">
-        <v>4.45</v>
-      </c>
-      <c r="AV22">
-        <v>3.28</v>
-      </c>
-      <c r="AW22">
-        <v>2.41</v>
-      </c>
-      <c r="AX22">
-        <v>1.85</v>
-      </c>
-      <c r="AY22">
-        <v>1.58</v>
-      </c>
-      <c r="AZ22">
-        <v>0</v>
-      </c>
-      <c r="BA22">
-        <v>0</v>
-      </c>
-      <c r="BB22">
-        <v>1.8</v>
-      </c>
-      <c r="BC22">
-        <v>2.1</v>
-      </c>
-      <c r="BD22" s="3">
+        <v>241</v>
+      </c>
+      <c r="AL22" s="3">
         <v>45763.5</v>
       </c>
     </row>
-    <row r="23" spans="1:56">
+    <row r="23" spans="1:38">
       <c r="A23" s="2">
         <v>45763</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="F23" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="G23">
         <v>3</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I23">
         <v>1</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K23" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L23">
-        <v>2.58</v>
+        <v>2.15</v>
       </c>
       <c r="M23">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N23">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="O23">
+        <v>1.57</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>2.6</v>
+      </c>
+      <c r="R23">
+        <v>1.38</v>
+      </c>
+      <c r="S23">
+        <v>2.8</v>
+      </c>
+      <c r="T23">
+        <v>2.8</v>
+      </c>
+      <c r="U23">
+        <v>1.4</v>
+      </c>
+      <c r="V23">
+        <v>7</v>
+      </c>
+      <c r="W23">
+        <v>1.07</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
+        <v>9</v>
+      </c>
+      <c r="Z23">
+        <v>1.27</v>
+      </c>
+      <c r="AA23">
+        <v>3.3</v>
+      </c>
+      <c r="AB23">
+        <v>1.91</v>
+      </c>
+      <c r="AC23">
         <v>1.83</v>
       </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>2.2</v>
-      </c>
-      <c r="R23">
-        <v>1.48</v>
-      </c>
-      <c r="S23">
-        <v>2.5</v>
-      </c>
-      <c r="T23">
-        <v>3.2</v>
-      </c>
-      <c r="U23">
-        <v>1.3</v>
-      </c>
-      <c r="V23">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W23">
-        <v>1.05</v>
-      </c>
-      <c r="X23">
-        <v>1.01</v>
-      </c>
-      <c r="Y23">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z23">
-        <v>1.35</v>
-      </c>
-      <c r="AA23">
-        <v>2.75</v>
-      </c>
-      <c r="AB23">
-        <v>2.2</v>
-      </c>
-      <c r="AC23">
-        <v>1.61</v>
-      </c>
       <c r="AD23">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="AE23">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AF23">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG23">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH23">
-        <v>9.1</v>
+        <v>5.8</v>
       </c>
       <c r="AI23">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AJ23" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="AK23" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL23">
-        <v>1.28</v>
-      </c>
-      <c r="AM23">
-        <v>0</v>
-      </c>
-      <c r="AN23">
-        <v>1.4</v>
-      </c>
-      <c r="AO23">
-        <v>11</v>
-      </c>
-      <c r="AP23">
-        <v>1.26</v>
-      </c>
-      <c r="AQ23">
-        <v>1.49</v>
-      </c>
-      <c r="AR23">
-        <v>2.05</v>
-      </c>
-      <c r="AS23">
-        <v>2.23</v>
-      </c>
-      <c r="AT23">
-        <v>2.88</v>
-      </c>
-      <c r="AU23">
-        <v>3.32</v>
-      </c>
-      <c r="AV23">
-        <v>2.48</v>
-      </c>
-      <c r="AW23">
-        <v>1.93</v>
-      </c>
-      <c r="AX23">
-        <v>1.59</v>
-      </c>
-      <c r="AY23">
-        <v>1.36</v>
-      </c>
-      <c r="AZ23">
-        <v>0</v>
-      </c>
-      <c r="BA23">
-        <v>0</v>
-      </c>
-      <c r="BB23">
-        <v>1.83</v>
-      </c>
-      <c r="BC23">
-        <v>2.2</v>
-      </c>
-      <c r="BD23" s="3">
+        <v>242</v>
+      </c>
+      <c r="AL23" s="3">
         <v>45763.5</v>
       </c>
     </row>
-    <row r="24" spans="1:56">
+    <row r="24" spans="1:38">
       <c r="A24" s="2">
         <v>45763</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E24" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="F24" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -5156,7 +3860,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L24">
         <v>6.2</v>
@@ -5231,120 +3935,66 @@
         <v>1.1</v>
       </c>
       <c r="AJ24" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="AK24" t="s">
-        <v>232</v>
-      </c>
-      <c r="AL24">
-        <v>2.4</v>
-      </c>
-      <c r="AM24">
-        <v>1.17</v>
-      </c>
-      <c r="AN24">
-        <v>1.1</v>
-      </c>
-      <c r="AO24">
-        <v>5</v>
-      </c>
-      <c r="AP24">
-        <v>0</v>
-      </c>
-      <c r="AQ24">
-        <v>0</v>
-      </c>
-      <c r="AR24">
-        <v>0</v>
-      </c>
-      <c r="AS24">
-        <v>0</v>
-      </c>
-      <c r="AT24">
-        <v>0</v>
-      </c>
-      <c r="AU24">
-        <v>0</v>
-      </c>
-      <c r="AV24">
-        <v>0</v>
-      </c>
-      <c r="AW24">
-        <v>0</v>
-      </c>
-      <c r="AX24">
-        <v>0</v>
-      </c>
-      <c r="AY24">
-        <v>0</v>
-      </c>
-      <c r="AZ24">
-        <v>0</v>
-      </c>
-      <c r="BA24">
-        <v>0</v>
-      </c>
-      <c r="BB24">
-        <v>3.1</v>
-      </c>
-      <c r="BC24">
-        <v>1.44</v>
-      </c>
-      <c r="BD24" s="3">
+        <v>213</v>
+      </c>
+      <c r="AL24" s="3">
         <v>45763.52083333334</v>
       </c>
     </row>
-    <row r="25" spans="1:56">
+    <row r="25" spans="1:38">
       <c r="A25" s="2">
         <v>45763</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D25" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E25" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="F25" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K25" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L25">
         <v>14</v>
       </c>
       <c r="M25">
-        <v>3.77</v>
+        <v>8.6</v>
       </c>
       <c r="N25">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="O25">
-        <v>4.33</v>
+        <v>6.5</v>
       </c>
       <c r="P25">
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -5377,16 +4027,16 @@
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AC25">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AD25">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="AE25">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AF25">
         <v>0</v>
@@ -5395,93 +4045,39 @@
         <v>0</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="AJ25" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="AK25" t="s">
-        <v>261</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>0</v>
-      </c>
-      <c r="AN25">
-        <v>0</v>
-      </c>
-      <c r="AO25">
-        <v>8</v>
-      </c>
-      <c r="AP25">
-        <v>0</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25">
-        <v>0</v>
-      </c>
-      <c r="AV25">
-        <v>0</v>
-      </c>
-      <c r="AW25">
-        <v>0</v>
-      </c>
-      <c r="AX25">
-        <v>0</v>
-      </c>
-      <c r="AY25">
-        <v>0</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>4.33</v>
-      </c>
-      <c r="BC25">
-        <v>1.25</v>
-      </c>
-      <c r="BD25" s="3">
+        <v>243</v>
+      </c>
+      <c r="AL25" s="3">
         <v>45763.54166666666</v>
       </c>
     </row>
-    <row r="26" spans="1:56">
+    <row r="26" spans="1:38">
       <c r="A26" s="2">
         <v>45763</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E26" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="F26" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="G26">
         <v>3</v>
@@ -5496,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L26">
         <v>3.25</v>
@@ -5571,290 +4167,182 @@
         <v>1.12</v>
       </c>
       <c r="AJ26" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="AK26" t="s">
-        <v>262</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
-        <v>0</v>
-      </c>
-      <c r="AN26">
-        <v>0</v>
-      </c>
-      <c r="AO26">
-        <v>16</v>
-      </c>
-      <c r="AP26">
-        <v>0</v>
-      </c>
-      <c r="AQ26">
-        <v>0</v>
-      </c>
-      <c r="AR26">
-        <v>0</v>
-      </c>
-      <c r="AS26">
-        <v>0</v>
-      </c>
-      <c r="AT26">
-        <v>0</v>
-      </c>
-      <c r="AU26">
-        <v>0</v>
-      </c>
-      <c r="AV26">
-        <v>0</v>
-      </c>
-      <c r="AW26">
-        <v>0</v>
-      </c>
-      <c r="AX26">
-        <v>0</v>
-      </c>
-      <c r="AY26">
-        <v>0</v>
-      </c>
-      <c r="AZ26">
-        <v>0</v>
-      </c>
-      <c r="BA26">
-        <v>0</v>
-      </c>
-      <c r="BB26">
-        <v>2.38</v>
-      </c>
-      <c r="BC26">
-        <v>1.67</v>
-      </c>
-      <c r="BD26" s="3">
+        <v>244</v>
+      </c>
+      <c r="AL26" s="3">
         <v>45763.54166666666</v>
       </c>
     </row>
-    <row r="27" spans="1:56">
+    <row r="27" spans="1:38">
       <c r="A27" s="2">
         <v>45763</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="D27" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="E27" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="F27" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27" t="s">
+        <v>189</v>
+      </c>
+      <c r="L27">
+        <v>1.65</v>
+      </c>
+      <c r="M27">
+        <v>3.95</v>
+      </c>
+      <c r="N27">
+        <v>6.8</v>
+      </c>
+      <c r="O27">
+        <v>1.36</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>3.4</v>
+      </c>
+      <c r="R27">
+        <v>1.33</v>
+      </c>
+      <c r="S27">
+        <v>2.94</v>
+      </c>
+      <c r="T27">
+        <v>2.55</v>
+      </c>
+      <c r="U27">
+        <v>1.43</v>
+      </c>
+      <c r="V27">
         <v>6</v>
       </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>4</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27" t="s">
-        <v>207</v>
-      </c>
-      <c r="L27">
-        <v>2.52</v>
-      </c>
-      <c r="M27">
-        <v>3.36</v>
-      </c>
-      <c r="N27">
-        <v>2.66</v>
-      </c>
-      <c r="O27">
-        <v>1.83</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>2.05</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB27">
+        <v>1.8</v>
+      </c>
+      <c r="AC27">
+        <v>2</v>
+      </c>
+      <c r="AD27">
+        <v>3</v>
+      </c>
+      <c r="AE27">
+        <v>1.38</v>
+      </c>
+      <c r="AF27">
         <v>1.85</v>
       </c>
-      <c r="AC27">
-        <v>1.89</v>
-      </c>
-      <c r="AD27">
-        <v>1.57</v>
-      </c>
-      <c r="AE27">
-        <v>2.2</v>
-      </c>
-      <c r="AF27">
-        <v>0</v>
-      </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH27">
-        <v>1.22</v>
+        <v>5</v>
       </c>
       <c r="AI27">
-        <v>3.9</v>
+        <v>1.12</v>
       </c>
       <c r="AJ27" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="AK27" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>0</v>
-      </c>
-      <c r="AN27">
-        <v>0</v>
-      </c>
-      <c r="AO27">
-        <v>14</v>
-      </c>
-      <c r="AP27">
-        <v>0</v>
-      </c>
-      <c r="AQ27">
-        <v>0</v>
-      </c>
-      <c r="AR27">
-        <v>0</v>
-      </c>
-      <c r="AS27">
-        <v>0</v>
-      </c>
-      <c r="AT27">
-        <v>0</v>
-      </c>
-      <c r="AU27">
-        <v>0</v>
-      </c>
-      <c r="AV27">
-        <v>0</v>
-      </c>
-      <c r="AW27">
-        <v>0</v>
-      </c>
-      <c r="AX27">
-        <v>0</v>
-      </c>
-      <c r="AY27">
-        <v>0</v>
-      </c>
-      <c r="AZ27">
-        <v>0</v>
-      </c>
-      <c r="BA27">
-        <v>0</v>
-      </c>
-      <c r="BB27">
-        <v>1.83</v>
-      </c>
-      <c r="BC27">
-        <v>2.05</v>
-      </c>
-      <c r="BD27" s="3">
+        <v>245</v>
+      </c>
+      <c r="AL27" s="3">
         <v>45763.54166666666</v>
       </c>
     </row>
-    <row r="28" spans="1:56">
+    <row r="28" spans="1:38">
       <c r="A28" s="2">
         <v>45763</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E28" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="F28" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>4</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
         <v>2</v>
       </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>1</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
       <c r="K28" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L28">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="M28">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="N28">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="O28">
-        <v>2.88</v>
+        <v>4.33</v>
       </c>
       <c r="P28">
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -5887,16 +4375,16 @@
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC28">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF28">
         <v>0</v>
@@ -5911,290 +4399,182 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="s">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="AK28" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>0</v>
-      </c>
-      <c r="AN28">
-        <v>0</v>
-      </c>
-      <c r="AO28">
-        <v>10</v>
-      </c>
-      <c r="AP28">
-        <v>0</v>
-      </c>
-      <c r="AQ28">
-        <v>0</v>
-      </c>
-      <c r="AR28">
-        <v>0</v>
-      </c>
-      <c r="AS28">
-        <v>0</v>
-      </c>
-      <c r="AT28">
-        <v>0</v>
-      </c>
-      <c r="AU28">
-        <v>0</v>
-      </c>
-      <c r="AV28">
-        <v>0</v>
-      </c>
-      <c r="AW28">
-        <v>0</v>
-      </c>
-      <c r="AX28">
-        <v>0</v>
-      </c>
-      <c r="AY28">
-        <v>0</v>
-      </c>
-      <c r="AZ28">
-        <v>0</v>
-      </c>
-      <c r="BA28">
-        <v>0</v>
-      </c>
-      <c r="BB28">
-        <v>2.88</v>
-      </c>
-      <c r="BC28">
-        <v>1.5</v>
-      </c>
-      <c r="BD28" s="3">
+        <v>246</v>
+      </c>
+      <c r="AL28" s="3">
         <v>45763.54166666666</v>
       </c>
     </row>
-    <row r="29" spans="1:56">
+    <row r="29" spans="1:38">
       <c r="A29" s="2">
         <v>45763</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="D29" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="E29" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="F29" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L29">
-        <v>1.65</v>
+        <v>2.52</v>
       </c>
       <c r="M29">
-        <v>3.95</v>
+        <v>3.36</v>
       </c>
       <c r="N29">
-        <v>6.8</v>
+        <v>2.66</v>
       </c>
       <c r="O29">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="P29">
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="R29">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC29">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AD29">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="AE29">
-        <v>1.38</v>
+        <v>2.2</v>
       </c>
       <c r="AF29">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AH29">
-        <v>5</v>
+        <v>1.22</v>
       </c>
       <c r="AI29">
-        <v>1.12</v>
+        <v>3.9</v>
       </c>
       <c r="AJ29" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="AK29" t="s">
-        <v>263</v>
-      </c>
-      <c r="AL29">
-        <v>1.24</v>
-      </c>
-      <c r="AM29">
-        <v>0</v>
-      </c>
-      <c r="AN29">
-        <v>2</v>
-      </c>
-      <c r="AO29">
-        <v>19</v>
-      </c>
-      <c r="AP29">
-        <v>1.14</v>
-      </c>
-      <c r="AQ29">
-        <v>1.27</v>
-      </c>
-      <c r="AR29">
-        <v>1.44</v>
-      </c>
-      <c r="AS29">
-        <v>1.8</v>
-      </c>
-      <c r="AT29">
-        <v>2.24</v>
-      </c>
-      <c r="AU29">
-        <v>4.6</v>
-      </c>
-      <c r="AV29">
-        <v>3.25</v>
-      </c>
-      <c r="AW29">
-        <v>2.43</v>
-      </c>
-      <c r="AX29">
-        <v>1.94</v>
-      </c>
-      <c r="AY29">
-        <v>1.61</v>
-      </c>
-      <c r="AZ29">
-        <v>0</v>
-      </c>
-      <c r="BA29">
-        <v>0</v>
-      </c>
-      <c r="BB29">
-        <v>1.36</v>
-      </c>
-      <c r="BC29">
-        <v>3.4</v>
-      </c>
-      <c r="BD29" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL29" s="3">
         <v>45763.54166666666</v>
       </c>
     </row>
-    <row r="30" spans="1:56">
+    <row r="30" spans="1:38">
       <c r="A30" s="2">
         <v>45763</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E30" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="F30" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="G30">
         <v>2</v>
       </c>
       <c r="H30">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I30">
         <v>1</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L30">
-        <v>14</v>
+        <v>4.1</v>
       </c>
       <c r="M30">
-        <v>8.6</v>
+        <v>3.8</v>
       </c>
       <c r="N30">
-        <v>1.14</v>
+        <v>1.65</v>
       </c>
       <c r="O30">
-        <v>6.5</v>
+        <v>2.88</v>
       </c>
       <c r="P30">
         <v>0</v>
       </c>
       <c r="Q30">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -6227,16 +4607,16 @@
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AC30">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AD30">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF30">
         <v>0</v>
@@ -6245,93 +4625,39 @@
         <v>0</v>
       </c>
       <c r="AH30">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI30">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="AK30" t="s">
-        <v>264</v>
-      </c>
-      <c r="AL30">
-        <v>0</v>
-      </c>
-      <c r="AM30">
-        <v>0</v>
-      </c>
-      <c r="AN30">
-        <v>0</v>
-      </c>
-      <c r="AO30">
-        <v>10</v>
-      </c>
-      <c r="AP30">
-        <v>0</v>
-      </c>
-      <c r="AQ30">
-        <v>0</v>
-      </c>
-      <c r="AR30">
-        <v>0</v>
-      </c>
-      <c r="AS30">
-        <v>0</v>
-      </c>
-      <c r="AT30">
-        <v>0</v>
-      </c>
-      <c r="AU30">
-        <v>0</v>
-      </c>
-      <c r="AV30">
-        <v>0</v>
-      </c>
-      <c r="AW30">
-        <v>0</v>
-      </c>
-      <c r="AX30">
-        <v>0</v>
-      </c>
-      <c r="AY30">
-        <v>0</v>
-      </c>
-      <c r="AZ30">
-        <v>0</v>
-      </c>
-      <c r="BA30">
-        <v>0</v>
-      </c>
-      <c r="BB30">
-        <v>6.5</v>
-      </c>
-      <c r="BC30">
-        <v>1.11</v>
-      </c>
-      <c r="BD30" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL30" s="3">
         <v>45763.54166666666</v>
       </c>
     </row>
-    <row r="31" spans="1:56">
+    <row r="31" spans="1:38">
       <c r="A31" s="2">
         <v>45763</v>
       </c>
       <c r="B31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" t="s">
         <v>70</v>
       </c>
-      <c r="C31" t="s">
-        <v>88</v>
-      </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E31" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="F31" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -6346,7 +4672,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L31">
         <v>2.06</v>
@@ -6421,120 +4747,66 @@
         <v>1.03</v>
       </c>
       <c r="AJ31" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="AK31" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL31">
-        <v>1.4</v>
-      </c>
-      <c r="AM31">
-        <v>0</v>
-      </c>
-      <c r="AN31">
-        <v>1.7</v>
-      </c>
-      <c r="AO31">
-        <v>4</v>
-      </c>
-      <c r="AP31">
-        <v>0</v>
-      </c>
-      <c r="AQ31">
-        <v>2</v>
-      </c>
-      <c r="AR31">
-        <v>0</v>
-      </c>
-      <c r="AS31">
-        <v>0</v>
-      </c>
-      <c r="AT31">
-        <v>0</v>
-      </c>
-      <c r="AU31">
-        <v>0</v>
-      </c>
-      <c r="AV31">
-        <v>1.8</v>
-      </c>
-      <c r="AW31">
-        <v>0</v>
-      </c>
-      <c r="AX31">
-        <v>0</v>
-      </c>
-      <c r="AY31">
-        <v>0</v>
-      </c>
-      <c r="AZ31">
-        <v>0</v>
-      </c>
-      <c r="BA31">
-        <v>0</v>
-      </c>
-      <c r="BB31">
-        <v>1.57</v>
-      </c>
-      <c r="BC31">
-        <v>3.1</v>
-      </c>
-      <c r="BD31" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL31" s="3">
         <v>45763.54861111111</v>
       </c>
     </row>
-    <row r="32" spans="1:56">
+    <row r="32" spans="1:38">
       <c r="A32" s="2">
         <v>45763</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E32" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="F32" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="G32">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L32">
-        <v>1.02</v>
+        <v>1.83</v>
       </c>
       <c r="M32">
-        <v>15</v>
+        <v>3.45</v>
       </c>
       <c r="N32">
-        <v>41</v>
+        <v>4.5</v>
       </c>
       <c r="O32">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="P32">
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>13</v>
+        <v>2.4</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -6555,28 +4827,28 @@
         <v>0</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB32">
-        <v>1.14</v>
+        <v>2.37</v>
       </c>
       <c r="AC32">
-        <v>5</v>
+        <v>1.53</v>
       </c>
       <c r="AD32">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AF32">
         <v>0</v>
@@ -6585,93 +4857,39 @@
         <v>0</v>
       </c>
       <c r="AH32">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI32">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="s">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="AK32" t="s">
-        <v>265</v>
-      </c>
-      <c r="AL32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>0</v>
-      </c>
-      <c r="AN32">
-        <v>0</v>
-      </c>
-      <c r="AO32">
-        <v>9</v>
-      </c>
-      <c r="AP32">
-        <v>0</v>
-      </c>
-      <c r="AQ32">
-        <v>0</v>
-      </c>
-      <c r="AR32">
-        <v>0</v>
-      </c>
-      <c r="AS32">
-        <v>0</v>
-      </c>
-      <c r="AT32">
-        <v>0</v>
-      </c>
-      <c r="AU32">
-        <v>0</v>
-      </c>
-      <c r="AV32">
-        <v>0</v>
-      </c>
-      <c r="AW32">
-        <v>0</v>
-      </c>
-      <c r="AX32">
-        <v>0</v>
-      </c>
-      <c r="AY32">
-        <v>0</v>
-      </c>
-      <c r="AZ32">
-        <v>0</v>
-      </c>
-      <c r="BA32">
-        <v>0</v>
-      </c>
-      <c r="BB32">
-        <v>1.04</v>
-      </c>
-      <c r="BC32">
-        <v>13</v>
-      </c>
-      <c r="BD32" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL32" s="3">
         <v>45763.58333333334</v>
       </c>
     </row>
-    <row r="33" spans="1:56">
+    <row r="33" spans="1:38">
       <c r="A33" s="2">
         <v>45763</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E33" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="F33" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="G33">
         <v>4</v>
@@ -6686,7 +4904,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L33">
         <v>1.7</v>
@@ -6761,163 +4979,109 @@
         <v>1.2</v>
       </c>
       <c r="AJ33" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="AK33" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL33">
-        <v>1.23</v>
-      </c>
-      <c r="AM33">
-        <v>1.22</v>
-      </c>
-      <c r="AN33">
-        <v>2.05</v>
-      </c>
-      <c r="AO33">
-        <v>5</v>
-      </c>
-      <c r="AP33">
-        <v>1.24</v>
-      </c>
-      <c r="AQ33">
-        <v>1.41</v>
-      </c>
-      <c r="AR33">
-        <v>1.67</v>
-      </c>
-      <c r="AS33">
-        <v>2.2</v>
-      </c>
-      <c r="AT33">
-        <v>2.78</v>
-      </c>
-      <c r="AU33">
-        <v>3.45</v>
-      </c>
-      <c r="AV33">
-        <v>2.65</v>
-      </c>
-      <c r="AW33">
-        <v>2</v>
-      </c>
-      <c r="AX33">
-        <v>1.55</v>
-      </c>
-      <c r="AY33">
-        <v>1.39</v>
-      </c>
-      <c r="AZ33">
-        <v>0</v>
-      </c>
-      <c r="BA33">
-        <v>0</v>
-      </c>
-      <c r="BB33">
-        <v>1.53</v>
-      </c>
-      <c r="BC33">
-        <v>2.75</v>
-      </c>
-      <c r="BD33" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL33" s="3">
         <v>45763.58333333334</v>
       </c>
     </row>
-    <row r="34" spans="1:56">
+    <row r="34" spans="1:38">
       <c r="A34" s="2">
         <v>45763</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E34" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="F34" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L34">
-        <v>1.83</v>
+        <v>1.02</v>
       </c>
       <c r="M34">
+        <v>15</v>
+      </c>
+      <c r="N34">
+        <v>41</v>
+      </c>
+      <c r="O34">
+        <v>1.04</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>13</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>1.14</v>
+      </c>
+      <c r="AC34">
+        <v>5</v>
+      </c>
+      <c r="AD34">
+        <v>1.21</v>
+      </c>
+      <c r="AE34">
         <v>3.45</v>
       </c>
-      <c r="N34">
-        <v>4.5</v>
-      </c>
-      <c r="O34">
-        <v>1.83</v>
-      </c>
-      <c r="P34">
-        <v>0</v>
-      </c>
-      <c r="Q34">
-        <v>2.4</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34">
-        <v>0</v>
-      </c>
-      <c r="V34">
-        <v>0</v>
-      </c>
-      <c r="W34">
-        <v>0</v>
-      </c>
-      <c r="X34">
-        <v>2.52</v>
-      </c>
-      <c r="Y34">
-        <v>1.49</v>
-      </c>
-      <c r="Z34">
-        <v>1.48</v>
-      </c>
-      <c r="AA34">
-        <v>2.37</v>
-      </c>
-      <c r="AB34">
-        <v>2.37</v>
-      </c>
-      <c r="AC34">
-        <v>1.53</v>
-      </c>
-      <c r="AD34">
-        <v>0</v>
-      </c>
-      <c r="AE34">
-        <v>0</v>
-      </c>
       <c r="AF34">
         <v>0</v>
       </c>
@@ -6925,93 +5089,39 @@
         <v>0</v>
       </c>
       <c r="AH34">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI34">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ34" t="s">
         <v>218</v>
       </c>
       <c r="AK34" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL34">
-        <v>0</v>
-      </c>
-      <c r="AM34">
-        <v>0</v>
-      </c>
-      <c r="AN34">
-        <v>0</v>
-      </c>
-      <c r="AO34">
-        <v>7</v>
-      </c>
-      <c r="AP34">
-        <v>0</v>
-      </c>
-      <c r="AQ34">
-        <v>0</v>
-      </c>
-      <c r="AR34">
-        <v>0</v>
-      </c>
-      <c r="AS34">
-        <v>0</v>
-      </c>
-      <c r="AT34">
-        <v>0</v>
-      </c>
-      <c r="AU34">
-        <v>0</v>
-      </c>
-      <c r="AV34">
-        <v>0</v>
-      </c>
-      <c r="AW34">
-        <v>0</v>
-      </c>
-      <c r="AX34">
-        <v>0</v>
-      </c>
-      <c r="AY34">
-        <v>0</v>
-      </c>
-      <c r="AZ34">
-        <v>0</v>
-      </c>
-      <c r="BA34">
-        <v>0</v>
-      </c>
-      <c r="BB34">
-        <v>1.83</v>
-      </c>
-      <c r="BC34">
-        <v>2.4</v>
-      </c>
-      <c r="BD34" s="3">
+        <v>247</v>
+      </c>
+      <c r="AL34" s="3">
         <v>45763.58333333334</v>
       </c>
     </row>
-    <row r="35" spans="1:56">
+    <row r="35" spans="1:38">
       <c r="A35" s="2">
         <v>45763</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E35" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="F35" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="G35">
         <v>5</v>
@@ -7026,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L35">
         <v>1.65</v>
@@ -7101,87 +5211,33 @@
         <v>1.11</v>
       </c>
       <c r="AJ35" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="AK35" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL35">
-        <v>1.22</v>
-      </c>
-      <c r="AM35">
-        <v>1.26</v>
-      </c>
-      <c r="AN35">
-        <v>1.95</v>
-      </c>
-      <c r="AO35">
-        <v>9</v>
-      </c>
-      <c r="AP35">
-        <v>1.19</v>
-      </c>
-      <c r="AQ35">
-        <v>1.33</v>
-      </c>
-      <c r="AR35">
-        <v>1.56</v>
-      </c>
-      <c r="AS35">
-        <v>1.89</v>
-      </c>
-      <c r="AT35">
-        <v>2.33</v>
-      </c>
-      <c r="AU35">
-        <v>4.1</v>
-      </c>
-      <c r="AV35">
-        <v>2.95</v>
-      </c>
-      <c r="AW35">
-        <v>2.23</v>
-      </c>
-      <c r="AX35">
-        <v>1.8</v>
-      </c>
-      <c r="AY35">
-        <v>1.52</v>
-      </c>
-      <c r="AZ35">
-        <v>0</v>
-      </c>
-      <c r="BA35">
-        <v>0</v>
-      </c>
-      <c r="BB35">
-        <v>1.5</v>
-      </c>
-      <c r="BC35">
-        <v>2.75</v>
-      </c>
-      <c r="BD35" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL35" s="3">
         <v>45763.64583333334</v>
       </c>
     </row>
-    <row r="36" spans="1:56">
+    <row r="36" spans="1:38">
       <c r="A36" s="2">
         <v>45763</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D36" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E36" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="F36" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -7196,7 +5252,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L36">
         <v>1.8</v>
@@ -7271,87 +5327,33 @@
         <v>1.11</v>
       </c>
       <c r="AJ36" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="AK36" t="s">
-        <v>266</v>
-      </c>
-      <c r="AL36">
-        <v>1.25</v>
-      </c>
-      <c r="AM36">
-        <v>1.3</v>
-      </c>
-      <c r="AN36">
-        <v>2.42</v>
-      </c>
-      <c r="AO36">
-        <v>12</v>
-      </c>
-      <c r="AP36">
-        <v>0</v>
-      </c>
-      <c r="AQ36">
-        <v>0</v>
-      </c>
-      <c r="AR36">
-        <v>0</v>
-      </c>
-      <c r="AS36">
-        <v>1.9</v>
-      </c>
-      <c r="AT36">
-        <v>0</v>
-      </c>
-      <c r="AU36">
-        <v>0</v>
-      </c>
-      <c r="AV36">
-        <v>0</v>
-      </c>
-      <c r="AW36">
-        <v>0</v>
-      </c>
-      <c r="AX36">
-        <v>1.9</v>
-      </c>
-      <c r="AY36">
-        <v>0</v>
-      </c>
-      <c r="AZ36">
-        <v>0</v>
-      </c>
-      <c r="BA36">
-        <v>0</v>
-      </c>
-      <c r="BB36">
-        <v>1.75</v>
-      </c>
-      <c r="BC36">
-        <v>2.5</v>
-      </c>
-      <c r="BD36" s="3">
+        <v>248</v>
+      </c>
+      <c r="AL36" s="3">
         <v>45763.65625</v>
       </c>
     </row>
-    <row r="37" spans="1:56">
+    <row r="37" spans="1:38">
       <c r="A37" s="2">
         <v>45763</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="D37" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E37" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="F37" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -7366,7 +5368,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L37">
         <v>1.68</v>
@@ -7441,87 +5443,33 @@
         <v>1.21</v>
       </c>
       <c r="AJ37" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="AK37" t="s">
-        <v>267</v>
-      </c>
-      <c r="AL37">
-        <v>1.2</v>
-      </c>
-      <c r="AM37">
-        <v>1.24</v>
-      </c>
-      <c r="AN37">
-        <v>2.05</v>
-      </c>
-      <c r="AO37">
-        <v>14</v>
-      </c>
-      <c r="AP37">
-        <v>1.11</v>
-      </c>
-      <c r="AQ37">
-        <v>1.21</v>
-      </c>
-      <c r="AR37">
-        <v>1.37</v>
-      </c>
-      <c r="AS37">
-        <v>1.58</v>
-      </c>
-      <c r="AT37">
-        <v>1.89</v>
-      </c>
-      <c r="AU37">
-        <v>5.3</v>
-      </c>
-      <c r="AV37">
-        <v>3.8</v>
-      </c>
-      <c r="AW37">
-        <v>2.8</v>
-      </c>
-      <c r="AX37">
-        <v>2.18</v>
-      </c>
-      <c r="AY37">
-        <v>1.8</v>
-      </c>
-      <c r="AZ37">
-        <v>0</v>
-      </c>
-      <c r="BA37">
-        <v>0</v>
-      </c>
-      <c r="BB37">
-        <v>1.44</v>
-      </c>
-      <c r="BC37">
-        <v>2.88</v>
-      </c>
-      <c r="BD37" s="3">
+        <v>249</v>
+      </c>
+      <c r="AL37" s="3">
         <v>45763.66666666666</v>
       </c>
     </row>
-    <row r="38" spans="1:56">
+    <row r="38" spans="1:38">
       <c r="A38" s="2">
         <v>45763</v>
       </c>
       <c r="B38" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C38" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="D38" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E38" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="F38" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -7536,7 +5484,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L38">
         <v>2.7</v>
@@ -7611,87 +5559,33 @@
         <v>1.1</v>
       </c>
       <c r="AJ38" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="AK38" t="s">
-        <v>268</v>
-      </c>
-      <c r="AL38">
-        <v>1.49</v>
-      </c>
-      <c r="AM38">
-        <v>1.3</v>
-      </c>
-      <c r="AN38">
-        <v>1.46</v>
-      </c>
-      <c r="AO38">
-        <v>11</v>
-      </c>
-      <c r="AP38">
-        <v>1.28</v>
-      </c>
-      <c r="AQ38">
-        <v>1.49</v>
-      </c>
-      <c r="AR38">
-        <v>1.81</v>
-      </c>
-      <c r="AS38">
-        <v>2.25</v>
-      </c>
-      <c r="AT38">
-        <v>2.9</v>
-      </c>
-      <c r="AU38">
-        <v>3.2</v>
-      </c>
-      <c r="AV38">
-        <v>2.4</v>
-      </c>
-      <c r="AW38">
-        <v>1.88</v>
-      </c>
-      <c r="AX38">
-        <v>1.55</v>
-      </c>
-      <c r="AY38">
-        <v>1.34</v>
-      </c>
-      <c r="AZ38">
-        <v>0</v>
-      </c>
-      <c r="BA38">
-        <v>0</v>
-      </c>
-      <c r="BB38">
-        <v>1.83</v>
-      </c>
-      <c r="BC38">
-        <v>2.05</v>
-      </c>
-      <c r="BD38" s="3">
+        <v>250</v>
+      </c>
+      <c r="AL38" s="3">
         <v>45763.66666666666</v>
       </c>
     </row>
-    <row r="39" spans="1:56">
+    <row r="39" spans="1:38">
       <c r="A39" s="2">
         <v>45763</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="D39" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E39" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="F39" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -7706,7 +5600,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L39">
         <v>2</v>
@@ -7781,87 +5675,33 @@
         <v>1.02</v>
       </c>
       <c r="AJ39" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="AK39" t="s">
-        <v>269</v>
-      </c>
-      <c r="AL39">
-        <v>1.25</v>
-      </c>
-      <c r="AM39">
-        <v>1.28</v>
-      </c>
-      <c r="AN39">
-        <v>1.7</v>
-      </c>
-      <c r="AO39">
-        <v>4</v>
-      </c>
-      <c r="AP39">
-        <v>1.57</v>
-      </c>
-      <c r="AQ39">
-        <v>1.96</v>
-      </c>
-      <c r="AR39">
-        <v>3.02</v>
-      </c>
-      <c r="AS39">
-        <v>3.5</v>
-      </c>
-      <c r="AT39">
-        <v>3.9</v>
-      </c>
-      <c r="AU39">
-        <v>2.45</v>
-      </c>
-      <c r="AV39">
-        <v>1.89</v>
-      </c>
-      <c r="AW39">
-        <v>1.47</v>
-      </c>
-      <c r="AX39">
-        <v>1.26</v>
-      </c>
-      <c r="AY39">
-        <v>1.19</v>
-      </c>
-      <c r="AZ39">
-        <v>0</v>
-      </c>
-      <c r="BA39">
-        <v>0</v>
-      </c>
-      <c r="BB39">
-        <v>1.9</v>
-      </c>
-      <c r="BC39">
-        <v>2.3</v>
-      </c>
-      <c r="BD39" s="3">
+        <v>251</v>
+      </c>
+      <c r="AL39" s="3">
         <v>45763.66666666666</v>
       </c>
     </row>
-    <row r="40" spans="1:56">
+    <row r="40" spans="1:38">
       <c r="A40" s="2">
         <v>45763</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C40" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="D40" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E40" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="F40" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -7876,7 +5716,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L40">
         <v>2.3</v>
@@ -7951,87 +5791,33 @@
         <v>1.02</v>
       </c>
       <c r="AJ40" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="AK40" t="s">
-        <v>270</v>
-      </c>
-      <c r="AL40">
-        <v>1.37</v>
-      </c>
-      <c r="AM40">
-        <v>1.3</v>
-      </c>
-      <c r="AN40">
-        <v>1.57</v>
-      </c>
-      <c r="AO40">
-        <v>11</v>
-      </c>
-      <c r="AP40">
-        <v>1.47</v>
-      </c>
-      <c r="AQ40">
-        <v>1.86</v>
-      </c>
-      <c r="AR40">
-        <v>2.92</v>
-      </c>
-      <c r="AS40">
-        <v>3.2</v>
-      </c>
-      <c r="AT40">
-        <v>4.4</v>
-      </c>
-      <c r="AU40">
-        <v>2.35</v>
-      </c>
-      <c r="AV40">
-        <v>1.8</v>
-      </c>
-      <c r="AW40">
-        <v>1.5</v>
-      </c>
-      <c r="AX40">
-        <v>1.29</v>
-      </c>
-      <c r="AY40">
-        <v>1.18</v>
-      </c>
-      <c r="AZ40">
-        <v>0</v>
-      </c>
-      <c r="BA40">
-        <v>0</v>
-      </c>
-      <c r="BB40">
-        <v>1.85</v>
-      </c>
-      <c r="BC40">
-        <v>2.4</v>
-      </c>
-      <c r="BD40" s="3">
+        <v>252</v>
+      </c>
+      <c r="AL40" s="3">
         <v>45763.76041666666</v>
       </c>
     </row>
-    <row r="41" spans="1:56">
+    <row r="41" spans="1:38">
       <c r="A41" s="2">
         <v>45763</v>
       </c>
       <c r="B41" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C41" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D41" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E41" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="F41" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="G41">
         <v>2</v>
@@ -8046,7 +5832,7 @@
         <v>2</v>
       </c>
       <c r="K41" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L41">
         <v>1.77</v>
@@ -8121,433 +5907,271 @@
         <v>1.03</v>
       </c>
       <c r="AJ41" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="AK41" t="s">
-        <v>271</v>
-      </c>
-      <c r="AL41">
-        <v>1.3</v>
-      </c>
-      <c r="AM41">
-        <v>1.32</v>
-      </c>
-      <c r="AN41">
-        <v>2.1</v>
-      </c>
-      <c r="AO41">
-        <v>13</v>
-      </c>
-      <c r="AP41">
-        <v>1.36</v>
-      </c>
-      <c r="AQ41">
-        <v>1.62</v>
-      </c>
-      <c r="AR41">
-        <v>2.35</v>
-      </c>
-      <c r="AS41">
-        <v>2.5</v>
-      </c>
-      <c r="AT41">
-        <v>3.3</v>
-      </c>
-      <c r="AU41">
-        <v>2.88</v>
-      </c>
-      <c r="AV41">
-        <v>2.2</v>
-      </c>
-      <c r="AW41">
-        <v>1.73</v>
-      </c>
-      <c r="AX41">
-        <v>1.48</v>
-      </c>
-      <c r="AY41">
-        <v>1.29</v>
-      </c>
-      <c r="AZ41">
-        <v>0</v>
-      </c>
-      <c r="BA41">
-        <v>0</v>
-      </c>
-      <c r="BB41">
-        <v>1.57</v>
-      </c>
-      <c r="BC41">
-        <v>2.63</v>
-      </c>
-      <c r="BD41" s="3">
+        <v>253</v>
+      </c>
+      <c r="AL41" s="3">
         <v>45763.77083333334</v>
       </c>
     </row>
-    <row r="42" spans="1:56">
+    <row r="42" spans="1:38">
       <c r="A42" s="2">
         <v>45763</v>
       </c>
       <c r="B42" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="C42" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D42" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E42" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="F42" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H42">
         <v>1</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" t="s">
+        <v>189</v>
+      </c>
+      <c r="L42">
+        <v>2.43</v>
+      </c>
+      <c r="M42">
+        <v>3</v>
+      </c>
+      <c r="N42">
+        <v>3</v>
+      </c>
+      <c r="O42">
+        <v>2.3</v>
+      </c>
+      <c r="P42">
+        <v>7.25</v>
+      </c>
+      <c r="Q42">
+        <v>1.8</v>
+      </c>
+      <c r="R42">
+        <v>1.55</v>
+      </c>
+      <c r="S42">
+        <v>2.53</v>
+      </c>
+      <c r="T42">
+        <v>3.45</v>
+      </c>
+      <c r="U42">
+        <v>1.34</v>
+      </c>
+      <c r="V42">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="W42">
+        <v>1.03</v>
+      </c>
+      <c r="X42">
+        <v>1.1</v>
+      </c>
+      <c r="Y42">
+        <v>6.2</v>
+      </c>
+      <c r="Z42">
+        <v>1.49</v>
+      </c>
+      <c r="AA42">
+        <v>2.5</v>
+      </c>
+      <c r="AB42">
+        <v>2.6</v>
+      </c>
+      <c r="AC42">
+        <v>1.47</v>
+      </c>
+      <c r="AD42">
+        <v>4.75</v>
+      </c>
+      <c r="AE42">
+        <v>1.16</v>
+      </c>
+      <c r="AF42">
+        <v>2.05</v>
+      </c>
+      <c r="AG42">
+        <v>1.73</v>
+      </c>
+      <c r="AH42">
+        <v>13</v>
+      </c>
+      <c r="AI42">
         <v>1</v>
       </c>
-      <c r="K42" t="s">
-        <v>207</v>
-      </c>
-      <c r="L42">
-        <v>2.13</v>
-      </c>
-      <c r="M42">
-        <v>3.3</v>
-      </c>
-      <c r="N42">
-        <v>3.72</v>
-      </c>
-      <c r="O42">
-        <v>1.73</v>
-      </c>
-      <c r="P42">
-        <v>7.5</v>
-      </c>
-      <c r="Q42">
-        <v>2.4</v>
-      </c>
-      <c r="R42">
-        <v>1.42</v>
-      </c>
-      <c r="S42">
-        <v>2.87</v>
-      </c>
-      <c r="T42">
-        <v>3.19</v>
-      </c>
-      <c r="U42">
-        <v>1.35</v>
-      </c>
-      <c r="V42">
-        <v>7.6</v>
-      </c>
-      <c r="W42">
-        <v>1.07</v>
-      </c>
-      <c r="X42">
-        <v>1.05</v>
-      </c>
-      <c r="Y42">
-        <v>7.8</v>
-      </c>
-      <c r="Z42">
-        <v>1.36</v>
-      </c>
-      <c r="AA42">
-        <v>3.17</v>
-      </c>
-      <c r="AB42">
-        <v>2.23</v>
-      </c>
-      <c r="AC42">
-        <v>1.67</v>
-      </c>
-      <c r="AD42">
-        <v>3.64</v>
-      </c>
-      <c r="AE42">
-        <v>1.22</v>
-      </c>
-      <c r="AF42">
-        <v>1.85</v>
-      </c>
-      <c r="AG42">
-        <v>1.85</v>
-      </c>
-      <c r="AH42">
-        <v>7.5</v>
-      </c>
-      <c r="AI42">
-        <v>1.05</v>
-      </c>
       <c r="AJ42" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="AK42" t="s">
-        <v>272</v>
-      </c>
-      <c r="AL42">
-        <v>1.28</v>
-      </c>
-      <c r="AM42">
-        <v>1.34</v>
-      </c>
-      <c r="AN42">
-        <v>1.73</v>
-      </c>
-      <c r="AO42">
-        <v>12</v>
-      </c>
-      <c r="AP42">
-        <v>1.13</v>
-      </c>
-      <c r="AQ42">
-        <v>1.22</v>
-      </c>
-      <c r="AR42">
-        <v>1.58</v>
-      </c>
-      <c r="AS42">
-        <v>1.75</v>
-      </c>
-      <c r="AT42">
-        <v>2.2</v>
-      </c>
-      <c r="AU42">
-        <v>4.75</v>
-      </c>
-      <c r="AV42">
-        <v>3.35</v>
-      </c>
-      <c r="AW42">
-        <v>2.4</v>
-      </c>
-      <c r="AX42">
-        <v>1.95</v>
-      </c>
-      <c r="AY42">
-        <v>1.62</v>
-      </c>
-      <c r="AZ42">
-        <v>0</v>
-      </c>
-      <c r="BA42">
-        <v>0</v>
-      </c>
-      <c r="BB42">
-        <v>1.73</v>
-      </c>
-      <c r="BC42">
-        <v>2.4</v>
-      </c>
-      <c r="BD42" s="3">
+        <v>254</v>
+      </c>
+      <c r="AL42" s="3">
         <v>45763.79166666666</v>
       </c>
     </row>
-    <row r="43" spans="1:56">
+    <row r="43" spans="1:38">
       <c r="A43" s="2">
         <v>45763</v>
       </c>
       <c r="B43" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="C43" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D43" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E43" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="F43" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="G43">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L43">
-        <v>2.43</v>
+        <v>2.13</v>
       </c>
       <c r="M43">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N43">
-        <v>3</v>
+        <v>3.72</v>
       </c>
       <c r="O43">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="P43">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="Q43">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="R43">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="S43">
-        <v>2.53</v>
+        <v>2.87</v>
       </c>
       <c r="T43">
-        <v>3.45</v>
+        <v>3.19</v>
       </c>
       <c r="U43">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V43">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="W43">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X43">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y43">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="Z43">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AA43">
-        <v>2.5</v>
+        <v>3.17</v>
       </c>
       <c r="AB43">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="AC43">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="AD43">
-        <v>4.75</v>
+        <v>3.64</v>
       </c>
       <c r="AE43">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF43">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG43">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AH43">
-        <v>13</v>
+        <v>7.5</v>
       </c>
       <c r="AI43">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AJ43" t="s">
-        <v>242</v>
+        <v>200</v>
       </c>
       <c r="AK43" t="s">
-        <v>273</v>
-      </c>
-      <c r="AL43">
-        <v>1.4</v>
-      </c>
-      <c r="AM43">
-        <v>1.35</v>
-      </c>
-      <c r="AN43">
-        <v>1.53</v>
-      </c>
-      <c r="AO43">
-        <v>9</v>
-      </c>
-      <c r="AP43">
-        <v>1.25</v>
-      </c>
-      <c r="AQ43">
-        <v>1.44</v>
-      </c>
-      <c r="AR43">
-        <v>1.7</v>
-      </c>
-      <c r="AS43">
-        <v>2.1</v>
-      </c>
-      <c r="AT43">
-        <v>2.62</v>
-      </c>
-      <c r="AU43">
-        <v>3.45</v>
-      </c>
-      <c r="AV43">
-        <v>2.62</v>
-      </c>
-      <c r="AW43">
-        <v>1.98</v>
-      </c>
-      <c r="AX43">
-        <v>1.67</v>
-      </c>
-      <c r="AY43">
-        <v>1.42</v>
-      </c>
-      <c r="AZ43">
-        <v>0</v>
-      </c>
-      <c r="BA43">
-        <v>0</v>
-      </c>
-      <c r="BB43">
-        <v>2.3</v>
-      </c>
-      <c r="BC43">
-        <v>1.8</v>
-      </c>
-      <c r="BD43" s="3">
+        <v>255</v>
+      </c>
+      <c r="AL43" s="3">
         <v>45763.79166666666</v>
       </c>
     </row>
-    <row r="44" spans="1:56">
+    <row r="44" spans="1:38">
       <c r="A44" s="2">
         <v>45763</v>
       </c>
       <c r="B44" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C44" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D44" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E44" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="F44" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="G44">
         <v>0</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -8556,168 +6180,114 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L44">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="M44">
+        <v>2.95</v>
+      </c>
+      <c r="N44">
+        <v>4.2</v>
+      </c>
+      <c r="O44">
+        <v>1.5</v>
+      </c>
+      <c r="P44">
+        <v>8</v>
+      </c>
+      <c r="Q44">
         <v>3</v>
       </c>
-      <c r="N44">
-        <v>2.8</v>
-      </c>
-      <c r="O44">
-        <v>1.8</v>
-      </c>
-      <c r="P44">
-        <v>7.25</v>
-      </c>
-      <c r="Q44">
-        <v>2.3</v>
-      </c>
       <c r="R44">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="S44">
         <v>2.4</v>
       </c>
       <c r="T44">
-        <v>3.3</v>
+        <v>3.77</v>
       </c>
       <c r="U44">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V44">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="W44">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X44">
         <v>1.1</v>
       </c>
       <c r="Y44">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="Z44">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AA44">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="AB44">
-        <v>2.45</v>
+        <v>2.71</v>
       </c>
       <c r="AC44">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AD44">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AE44">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF44">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG44">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AH44">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AI44">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ44" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="AK44" t="s">
-        <v>274</v>
-      </c>
-      <c r="AL44">
-        <v>1.34</v>
-      </c>
-      <c r="AM44">
-        <v>1.33</v>
-      </c>
-      <c r="AN44">
-        <v>1.46</v>
-      </c>
-      <c r="AO44">
-        <v>7</v>
-      </c>
-      <c r="AP44">
-        <v>1.33</v>
-      </c>
-      <c r="AQ44">
-        <v>1.57</v>
-      </c>
-      <c r="AR44">
-        <v>1.91</v>
-      </c>
-      <c r="AS44">
-        <v>2.39</v>
-      </c>
-      <c r="AT44">
-        <v>2.9</v>
-      </c>
-      <c r="AU44">
-        <v>3.15</v>
-      </c>
-      <c r="AV44">
-        <v>2.25</v>
-      </c>
-      <c r="AW44">
-        <v>1.8</v>
-      </c>
-      <c r="AX44">
-        <v>1.5</v>
-      </c>
-      <c r="AY44">
-        <v>1.29</v>
-      </c>
-      <c r="AZ44">
-        <v>0</v>
-      </c>
-      <c r="BA44">
-        <v>0</v>
-      </c>
-      <c r="BB44">
-        <v>1.8</v>
-      </c>
-      <c r="BC44">
-        <v>2.3</v>
-      </c>
-      <c r="BD44" s="3">
+        <v>256</v>
+      </c>
+      <c r="AL44" s="3">
         <v>45763.8125</v>
       </c>
     </row>
-    <row r="45" spans="1:56">
+    <row r="45" spans="1:38">
       <c r="A45" s="2">
         <v>45763</v>
       </c>
       <c r="B45" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C45" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D45" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E45" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="F45" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="G45">
         <v>0</v>
       </c>
       <c r="H45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -8726,502 +6296,340 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L45">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="M45">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N45">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="O45">
+        <v>1.8</v>
+      </c>
+      <c r="P45">
+        <v>7.25</v>
+      </c>
+      <c r="Q45">
+        <v>2.3</v>
+      </c>
+      <c r="R45">
         <v>1.5</v>
-      </c>
-      <c r="P45">
-        <v>8</v>
-      </c>
-      <c r="Q45">
-        <v>3</v>
-      </c>
-      <c r="R45">
-        <v>1.61</v>
       </c>
       <c r="S45">
         <v>2.4</v>
       </c>
       <c r="T45">
-        <v>3.77</v>
+        <v>3.3</v>
       </c>
       <c r="U45">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V45">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="W45">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X45">
         <v>1.1</v>
       </c>
       <c r="Y45">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="Z45">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AA45">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="AB45">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="AC45">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AD45">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AE45">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF45">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG45">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AH45">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AI45">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ45" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="AK45" t="s">
-        <v>275</v>
-      </c>
-      <c r="AL45">
-        <v>1.38</v>
-      </c>
-      <c r="AM45">
-        <v>1.28</v>
-      </c>
-      <c r="AN45">
-        <v>1.75</v>
-      </c>
-      <c r="AO45">
-        <v>11</v>
-      </c>
-      <c r="AP45">
-        <v>1.25</v>
-      </c>
-      <c r="AQ45">
-        <v>1.37</v>
-      </c>
-      <c r="AR45">
-        <v>1.88</v>
-      </c>
-      <c r="AS45">
-        <v>2.1</v>
-      </c>
-      <c r="AT45">
-        <v>2.63</v>
-      </c>
-      <c r="AU45">
-        <v>3.7</v>
-      </c>
-      <c r="AV45">
-        <v>2.67</v>
-      </c>
-      <c r="AW45">
-        <v>2.09</v>
-      </c>
-      <c r="AX45">
-        <v>1.69</v>
-      </c>
-      <c r="AY45">
-        <v>1.43</v>
-      </c>
-      <c r="AZ45">
-        <v>0</v>
-      </c>
-      <c r="BA45">
-        <v>0</v>
-      </c>
-      <c r="BB45">
-        <v>1.5</v>
-      </c>
-      <c r="BC45">
-        <v>3</v>
-      </c>
-      <c r="BD45" s="3">
+        <v>257</v>
+      </c>
+      <c r="AL45" s="3">
         <v>45763.8125</v>
       </c>
     </row>
-    <row r="46" spans="1:56">
+    <row r="46" spans="1:38">
       <c r="A46" s="2">
         <v>45763</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D46" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E46" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="F46" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L46">
+        <v>2.1</v>
+      </c>
+      <c r="M46">
+        <v>2.75</v>
+      </c>
+      <c r="N46">
+        <v>3.8</v>
+      </c>
+      <c r="O46">
         <v>1.73</v>
       </c>
-      <c r="M46">
-        <v>3.5</v>
-      </c>
-      <c r="N46">
-        <v>4.7</v>
-      </c>
-      <c r="O46">
+      <c r="P46">
+        <v>6.8</v>
+      </c>
+      <c r="Q46">
+        <v>2.64</v>
+      </c>
+      <c r="R46">
         <v>1.64</v>
       </c>
-      <c r="P46">
-        <v>7.6</v>
-      </c>
-      <c r="Q46">
-        <v>2.75</v>
-      </c>
-      <c r="R46">
-        <v>1.44</v>
-      </c>
       <c r="S46">
-        <v>2.78</v>
+        <v>2.31</v>
       </c>
       <c r="T46">
-        <v>3.17</v>
+        <v>3.8</v>
       </c>
       <c r="U46">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="V46">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W46">
         <v>1.03</v>
       </c>
       <c r="X46">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y46">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="Z46">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AA46">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="AB46">
-        <v>2.1</v>
+        <v>2.91</v>
       </c>
       <c r="AC46">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AD46">
-        <v>3.77</v>
+        <v>4.7</v>
       </c>
       <c r="AE46">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AF46">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AG46">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AH46">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="AI46">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AJ46" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="AK46" t="s">
-        <v>276</v>
-      </c>
-      <c r="AL46">
-        <v>1.3</v>
-      </c>
-      <c r="AM46">
-        <v>1.3</v>
-      </c>
-      <c r="AN46">
-        <v>2.05</v>
-      </c>
-      <c r="AO46">
-        <v>10</v>
-      </c>
-      <c r="AP46">
-        <v>1.16</v>
-      </c>
-      <c r="AQ46">
-        <v>1.26</v>
-      </c>
-      <c r="AR46">
-        <v>1.49</v>
-      </c>
-      <c r="AS46">
-        <v>1.85</v>
-      </c>
-      <c r="AT46">
-        <v>2.4</v>
-      </c>
-      <c r="AU46">
-        <v>4.4</v>
-      </c>
-      <c r="AV46">
-        <v>3.22</v>
-      </c>
-      <c r="AW46">
-        <v>2.38</v>
-      </c>
-      <c r="AX46">
-        <v>1.85</v>
-      </c>
-      <c r="AY46">
-        <v>1.57</v>
-      </c>
-      <c r="AZ46">
-        <v>0</v>
-      </c>
-      <c r="BA46">
-        <v>0</v>
-      </c>
-      <c r="BB46">
-        <v>1.64</v>
-      </c>
-      <c r="BC46">
-        <v>2.75</v>
-      </c>
-      <c r="BD46" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL46" s="3">
         <v>45763.83333333334</v>
       </c>
     </row>
-    <row r="47" spans="1:56">
+    <row r="47" spans="1:38">
       <c r="A47" s="2">
         <v>45763</v>
       </c>
       <c r="B47" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D47" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E47" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="F47" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K47" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L47">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="M47">
+        <v>3.5</v>
+      </c>
+      <c r="N47">
+        <v>4.7</v>
+      </c>
+      <c r="O47">
+        <v>1.64</v>
+      </c>
+      <c r="P47">
+        <v>7.6</v>
+      </c>
+      <c r="Q47">
         <v>2.75</v>
       </c>
-      <c r="N47">
-        <v>3.8</v>
-      </c>
-      <c r="O47">
-        <v>1.73</v>
-      </c>
-      <c r="P47">
-        <v>6.8</v>
-      </c>
-      <c r="Q47">
-        <v>2.64</v>
-      </c>
       <c r="R47">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="S47">
-        <v>2.31</v>
+        <v>2.78</v>
       </c>
       <c r="T47">
-        <v>3.8</v>
+        <v>3.17</v>
       </c>
       <c r="U47">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="V47">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W47">
         <v>1.03</v>
       </c>
       <c r="X47">
+        <v>1.04</v>
+      </c>
+      <c r="Y47">
+        <v>8.5</v>
+      </c>
+      <c r="Z47">
+        <v>1.35</v>
+      </c>
+      <c r="AA47">
+        <v>3</v>
+      </c>
+      <c r="AB47">
+        <v>2.1</v>
+      </c>
+      <c r="AC47">
+        <v>1.7</v>
+      </c>
+      <c r="AD47">
+        <v>3.77</v>
+      </c>
+      <c r="AE47">
+        <v>1.25</v>
+      </c>
+      <c r="AF47">
+        <v>1.95</v>
+      </c>
+      <c r="AG47">
+        <v>1.8</v>
+      </c>
+      <c r="AH47">
+        <v>6.5</v>
+      </c>
+      <c r="AI47">
         <v>1.08</v>
       </c>
-      <c r="Y47">
-        <v>6.2</v>
-      </c>
-      <c r="Z47">
-        <v>1.57</v>
-      </c>
-      <c r="AA47">
-        <v>2.29</v>
-      </c>
-      <c r="AB47">
-        <v>2.91</v>
-      </c>
-      <c r="AC47">
-        <v>1.4</v>
-      </c>
-      <c r="AD47">
-        <v>4.7</v>
-      </c>
-      <c r="AE47">
-        <v>1.14</v>
-      </c>
-      <c r="AF47">
-        <v>2.2</v>
-      </c>
-      <c r="AG47">
-        <v>1.62</v>
-      </c>
-      <c r="AH47">
-        <v>11.5</v>
-      </c>
-      <c r="AI47">
-        <v>1.03</v>
-      </c>
       <c r="AJ47" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="AK47" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL47">
-        <v>1.4</v>
-      </c>
-      <c r="AM47">
-        <v>1.35</v>
-      </c>
-      <c r="AN47">
-        <v>1.67</v>
-      </c>
-      <c r="AO47">
-        <v>10</v>
-      </c>
-      <c r="AP47">
-        <v>1.2</v>
-      </c>
-      <c r="AQ47">
-        <v>1.29</v>
-      </c>
-      <c r="AR47">
-        <v>1.76</v>
-      </c>
-      <c r="AS47">
-        <v>1.96</v>
-      </c>
-      <c r="AT47">
-        <v>2.65</v>
-      </c>
-      <c r="AU47">
-        <v>3.7</v>
-      </c>
-      <c r="AV47">
-        <v>2.87</v>
-      </c>
-      <c r="AW47">
-        <v>2.23</v>
-      </c>
-      <c r="AX47">
-        <v>1.78</v>
-      </c>
-      <c r="AY47">
-        <v>1.5</v>
-      </c>
-      <c r="AZ47">
-        <v>0</v>
-      </c>
-      <c r="BA47">
-        <v>0</v>
-      </c>
-      <c r="BB47">
-        <v>1.73</v>
-      </c>
-      <c r="BC47">
-        <v>2.64</v>
-      </c>
-      <c r="BD47" s="3">
+        <v>258</v>
+      </c>
+      <c r="AL47" s="3">
         <v>45763.83333333334</v>
       </c>
     </row>
-    <row r="48" spans="1:56">
+    <row r="48" spans="1:38">
       <c r="A48" s="2">
         <v>45763</v>
       </c>
       <c r="B48" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C48" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="D48" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E48" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="F48" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -9236,7 +6644,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L48">
         <v>3.47</v>
@@ -9311,87 +6719,33 @@
         <v>1.03</v>
       </c>
       <c r="AJ48" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="AK48" t="s">
-        <v>239</v>
-      </c>
-      <c r="AL48">
-        <v>1.33</v>
-      </c>
-      <c r="AM48">
-        <v>1.25</v>
-      </c>
-      <c r="AN48">
-        <v>1.09</v>
-      </c>
-      <c r="AO48">
-        <v>4</v>
-      </c>
-      <c r="AP48">
-        <v>1.48</v>
-      </c>
-      <c r="AQ48">
-        <v>1.75</v>
-      </c>
-      <c r="AR48">
-        <v>2.68</v>
-      </c>
-      <c r="AS48">
-        <v>2.9</v>
-      </c>
-      <c r="AT48">
-        <v>3.8</v>
-      </c>
-      <c r="AU48">
-        <v>2.5</v>
-      </c>
-      <c r="AV48">
-        <v>1.95</v>
-      </c>
-      <c r="AW48">
-        <v>1.57</v>
-      </c>
-      <c r="AX48">
-        <v>1.36</v>
-      </c>
-      <c r="AY48">
-        <v>1.18</v>
-      </c>
-      <c r="AZ48">
-        <v>0</v>
-      </c>
-      <c r="BA48">
-        <v>0</v>
-      </c>
-      <c r="BB48">
-        <v>2.4</v>
-      </c>
-      <c r="BC48">
-        <v>1.75</v>
-      </c>
-      <c r="BD48" s="3">
+        <v>221</v>
+      </c>
+      <c r="AL48" s="3">
         <v>45763.85416666666</v>
       </c>
     </row>
-    <row r="49" spans="1:56">
+    <row r="49" spans="1:38">
       <c r="A49" s="2">
         <v>45763</v>
       </c>
       <c r="B49" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C49" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D49" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E49" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="F49" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -9406,7 +6760,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L49">
         <v>2.62</v>
@@ -9481,576 +6835,360 @@
         <v>1</v>
       </c>
       <c r="AJ49" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="AK49" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL49">
-        <v>1.4</v>
-      </c>
-      <c r="AM49">
-        <v>1.34</v>
-      </c>
-      <c r="AN49">
-        <v>1.53</v>
-      </c>
-      <c r="AO49">
-        <v>9</v>
-      </c>
-      <c r="AP49">
-        <v>1.22</v>
-      </c>
-      <c r="AQ49">
-        <v>1.36</v>
-      </c>
-      <c r="AR49">
-        <v>1.62</v>
-      </c>
-      <c r="AS49">
-        <v>2.02</v>
-      </c>
-      <c r="AT49">
-        <v>2.4</v>
-      </c>
-      <c r="AU49">
-        <v>3.8</v>
-      </c>
-      <c r="AV49">
-        <v>2.88</v>
-      </c>
-      <c r="AW49">
-        <v>2.2</v>
-      </c>
-      <c r="AX49">
-        <v>1.75</v>
-      </c>
-      <c r="AY49">
-        <v>1.46</v>
-      </c>
-      <c r="AZ49">
-        <v>0</v>
-      </c>
-      <c r="BA49">
-        <v>0</v>
-      </c>
-      <c r="BB49">
-        <v>1.85</v>
-      </c>
-      <c r="BC49">
-        <v>2.43</v>
-      </c>
-      <c r="BD49" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL49" s="3">
         <v>45763.875</v>
       </c>
     </row>
-    <row r="50" spans="1:56">
+    <row r="50" spans="1:38">
       <c r="A50" s="2">
         <v>45763</v>
       </c>
       <c r="B50" t="s">
+        <v>64</v>
+      </c>
+      <c r="C50" t="s">
         <v>82</v>
       </c>
-      <c r="C50" t="s">
-        <v>100</v>
-      </c>
       <c r="D50" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E50" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="F50" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J50">
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L50">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="M50">
-        <v>3.05</v>
+        <v>6.5</v>
       </c>
       <c r="N50">
-        <v>3.1</v>
+        <v>13.93</v>
       </c>
       <c r="O50">
-        <v>2.1</v>
+        <v>1.22</v>
       </c>
       <c r="P50">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="Q50">
-        <v>2</v>
+        <v>4.75</v>
       </c>
       <c r="R50">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="S50">
+        <v>3.4</v>
+      </c>
+      <c r="T50">
+        <v>2.3</v>
+      </c>
+      <c r="U50">
+        <v>1.6</v>
+      </c>
+      <c r="V50">
+        <v>5.25</v>
+      </c>
+      <c r="W50">
+        <v>1.14</v>
+      </c>
+      <c r="X50">
+        <v>1.03</v>
+      </c>
+      <c r="Y50">
+        <v>14</v>
+      </c>
+      <c r="Z50">
+        <v>1.15</v>
+      </c>
+      <c r="AA50">
+        <v>4.45</v>
+      </c>
+      <c r="AB50">
+        <v>1.63</v>
+      </c>
+      <c r="AC50">
         <v>2.25</v>
       </c>
-      <c r="T50">
-        <v>3.63</v>
-      </c>
-      <c r="U50">
-        <v>1.28</v>
-      </c>
-      <c r="V50">
-        <v>9.75</v>
-      </c>
-      <c r="W50">
-        <v>1.01</v>
-      </c>
-      <c r="X50">
-        <v>1.1</v>
-      </c>
-      <c r="Y50">
-        <v>6</v>
-      </c>
-      <c r="Z50">
-        <v>1.44</v>
-      </c>
-      <c r="AA50">
-        <v>2.5</v>
-      </c>
-      <c r="AB50">
-        <v>2.52</v>
-      </c>
-      <c r="AC50">
-        <v>1.5</v>
-      </c>
       <c r="AD50">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="AE50">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="AF50">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AG50">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AH50">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="AI50">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AJ50" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="AK50" t="s">
-        <v>277</v>
-      </c>
-      <c r="AL50">
-        <v>1.33</v>
-      </c>
-      <c r="AM50">
-        <v>1.3</v>
-      </c>
-      <c r="AN50">
-        <v>1.55</v>
-      </c>
-      <c r="AO50">
-        <v>10</v>
-      </c>
-      <c r="AP50">
-        <v>1.22</v>
-      </c>
-      <c r="AQ50">
-        <v>1.43</v>
-      </c>
-      <c r="AR50">
-        <v>1.9</v>
-      </c>
-      <c r="AS50">
-        <v>1.98</v>
-      </c>
-      <c r="AT50">
-        <v>2.67</v>
-      </c>
-      <c r="AU50">
-        <v>3.62</v>
-      </c>
-      <c r="AV50">
-        <v>2.62</v>
-      </c>
-      <c r="AW50">
-        <v>2.1</v>
-      </c>
-      <c r="AX50">
-        <v>1.72</v>
-      </c>
-      <c r="AY50">
-        <v>1.46</v>
-      </c>
-      <c r="AZ50">
-        <v>0</v>
-      </c>
-      <c r="BA50">
-        <v>0</v>
-      </c>
-      <c r="BB50">
-        <v>2.1</v>
-      </c>
-      <c r="BC50">
-        <v>2</v>
-      </c>
-      <c r="BD50" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL50" s="3">
         <v>45763.89583333334</v>
       </c>
     </row>
-    <row r="51" spans="1:56">
+    <row r="51" spans="1:38">
       <c r="A51" s="2">
         <v>45763</v>
       </c>
       <c r="B51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51" t="s">
         <v>82</v>
       </c>
-      <c r="C51" t="s">
-        <v>100</v>
-      </c>
       <c r="D51" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E51" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="F51" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="G51">
         <v>2</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51" t="s">
+        <v>189</v>
+      </c>
+      <c r="L51">
+        <v>2.5</v>
+      </c>
+      <c r="M51">
+        <v>3.05</v>
+      </c>
+      <c r="N51">
+        <v>3.1</v>
+      </c>
+      <c r="O51">
+        <v>2.1</v>
+      </c>
+      <c r="P51">
+        <v>7.5</v>
+      </c>
+      <c r="Q51">
         <v>2</v>
       </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51" t="s">
-        <v>207</v>
-      </c>
-      <c r="L51">
-        <v>2.45</v>
-      </c>
-      <c r="M51">
-        <v>3.18</v>
-      </c>
-      <c r="N51">
-        <v>3</v>
-      </c>
-      <c r="O51">
-        <v>2.2</v>
-      </c>
-      <c r="P51">
-        <v>8</v>
-      </c>
-      <c r="Q51">
-        <v>1.83</v>
-      </c>
       <c r="R51">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="S51">
-        <v>2.61</v>
+        <v>2.25</v>
       </c>
       <c r="T51">
-        <v>3.3</v>
+        <v>3.63</v>
       </c>
       <c r="U51">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V51">
-        <v>9.199999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="W51">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y51">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z51">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AA51">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AB51">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="AC51">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AD51">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AE51">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF51">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AG51">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AH51">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="AI51">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ51" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="AK51" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL51">
-        <v>1.36</v>
-      </c>
-      <c r="AM51">
-        <v>1.28</v>
-      </c>
-      <c r="AN51">
-        <v>1.53</v>
-      </c>
-      <c r="AO51">
-        <v>9</v>
-      </c>
-      <c r="AP51">
-        <v>1.25</v>
-      </c>
-      <c r="AQ51">
-        <v>1.48</v>
-      </c>
-      <c r="AR51">
-        <v>2.05</v>
-      </c>
-      <c r="AS51">
-        <v>2.29</v>
-      </c>
-      <c r="AT51">
-        <v>2.9</v>
-      </c>
-      <c r="AU51">
-        <v>3.32</v>
-      </c>
-      <c r="AV51">
-        <v>2.44</v>
-      </c>
-      <c r="AW51">
-        <v>1.93</v>
-      </c>
-      <c r="AX51">
-        <v>1.58</v>
-      </c>
-      <c r="AY51">
-        <v>1.36</v>
-      </c>
-      <c r="AZ51">
-        <v>0</v>
-      </c>
-      <c r="BA51">
-        <v>0</v>
-      </c>
-      <c r="BB51">
-        <v>2.2</v>
-      </c>
-      <c r="BC51">
-        <v>1.83</v>
-      </c>
-      <c r="BD51" s="3">
+        <v>259</v>
+      </c>
+      <c r="AL51" s="3">
         <v>45763.89583333334</v>
       </c>
     </row>
-    <row r="52" spans="1:56">
+    <row r="52" spans="1:38">
       <c r="A52" s="2">
         <v>45763</v>
       </c>
       <c r="B52" t="s">
+        <v>64</v>
+      </c>
+      <c r="C52" t="s">
         <v>82</v>
       </c>
-      <c r="C52" t="s">
-        <v>100</v>
-      </c>
       <c r="D52" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E52" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="F52" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="G52">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H52">
         <v>0</v>
       </c>
       <c r="I52">
+        <v>2</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52" t="s">
+        <v>189</v>
+      </c>
+      <c r="L52">
+        <v>2.45</v>
+      </c>
+      <c r="M52">
+        <v>3.18</v>
+      </c>
+      <c r="N52">
         <v>3</v>
       </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52" t="s">
-        <v>207</v>
-      </c>
-      <c r="L52">
-        <v>1.2</v>
-      </c>
-      <c r="M52">
-        <v>6.5</v>
-      </c>
-      <c r="N52">
-        <v>13.93</v>
-      </c>
       <c r="O52">
-        <v>1.22</v>
+        <v>2.2</v>
       </c>
       <c r="P52">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q52">
-        <v>4.75</v>
+        <v>1.83</v>
       </c>
       <c r="R52">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="S52">
-        <v>3.4</v>
+        <v>2.61</v>
       </c>
       <c r="T52">
+        <v>3.3</v>
+      </c>
+      <c r="U52">
+        <v>1.32</v>
+      </c>
+      <c r="V52">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W52">
+        <v>1.04</v>
+      </c>
+      <c r="X52">
+        <v>1.02</v>
+      </c>
+      <c r="Y52">
+        <v>7</v>
+      </c>
+      <c r="Z52">
+        <v>1.4</v>
+      </c>
+      <c r="AA52">
+        <v>2.78</v>
+      </c>
+      <c r="AB52">
         <v>2.3</v>
       </c>
-      <c r="U52">
-        <v>1.6</v>
-      </c>
-      <c r="V52">
-        <v>5.25</v>
-      </c>
-      <c r="W52">
-        <v>1.14</v>
-      </c>
-      <c r="X52">
-        <v>1.03</v>
-      </c>
-      <c r="Y52">
-        <v>14</v>
-      </c>
-      <c r="Z52">
-        <v>1.15</v>
-      </c>
-      <c r="AA52">
-        <v>4.45</v>
-      </c>
-      <c r="AB52">
-        <v>1.63</v>
-      </c>
       <c r="AC52">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="AD52">
-        <v>2.45</v>
+        <v>4.65</v>
       </c>
       <c r="AE52">
-        <v>1.54</v>
+        <v>1.16</v>
       </c>
       <c r="AF52">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AG52">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="AH52">
-        <v>4.5</v>
+        <v>9.5</v>
       </c>
       <c r="AI52">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AJ52" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="AK52" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL52">
-        <v>1.13</v>
-      </c>
-      <c r="AM52">
-        <v>1.14</v>
-      </c>
-      <c r="AN52">
-        <v>4.4</v>
-      </c>
-      <c r="AO52">
-        <v>6</v>
-      </c>
-      <c r="AP52">
-        <v>1.18</v>
-      </c>
-      <c r="AQ52">
-        <v>1.35</v>
-      </c>
-      <c r="AR52">
-        <v>1.78</v>
-      </c>
-      <c r="AS52">
-        <v>1.97</v>
-      </c>
-      <c r="AT52">
-        <v>2.45</v>
-      </c>
-      <c r="AU52">
-        <v>4</v>
-      </c>
-      <c r="AV52">
-        <v>3</v>
-      </c>
-      <c r="AW52">
-        <v>2.22</v>
-      </c>
-      <c r="AX52">
-        <v>1.78</v>
-      </c>
-      <c r="AY52">
-        <v>1.49</v>
-      </c>
-      <c r="AZ52">
-        <v>0</v>
-      </c>
-      <c r="BA52">
-        <v>0</v>
-      </c>
-      <c r="BB52">
-        <v>1.22</v>
-      </c>
-      <c r="BC52">
-        <v>4.75</v>
-      </c>
-      <c r="BD52" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL52" s="3">
         <v>45763.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-04-16.xlsx
+++ b/jogos_2025-04-16.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,109 +643,109 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AA2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AB2" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>2.57</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['31', '45']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>['16', '39', '43', '62']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.35</v>
+        <v>2.08</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.73</v>
+        <v>2.46</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45763.29166666666</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,109 +772,109 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
-        <v>4</v>
-      </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="O3" t="n">
         <v>3</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="O3" t="n">
-        <v>4.15</v>
-      </c>
       <c r="P3" t="n">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.18</v>
+        <v>3.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>3.88</v>
+        <v>2.75</v>
       </c>
       <c r="T3" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="X3" t="n">
-        <v>5.6</v>
+        <v>3.25</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.73</v>
+        <v>1.79</v>
       </c>
       <c r="AA3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD3" t="n">
         <v>2</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.57</v>
-      </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>['31', '45']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['16', '39', '43', '62']</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>2.08</v>
+        <v>1.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.46</v>
+        <v>1.73</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45763.29166666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,19 +2320,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7</v>
+        <v>3.31</v>
       </c>
       <c r="N15" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA15" t="n">
         <v>3</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>7</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
         <v>1.47</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45763.47916666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,19 +2449,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X16" t="n">
         <v>2.05</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="Y16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['-1']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['-1']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
         <v>1.47</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45763.47916666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,106 +2578,106 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M17" t="n">
         <v>3</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.15</v>
-      </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="P17" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X17" t="n">
         <v>2.5</v>
       </c>
-      <c r="T17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U17" t="n">
+      <c r="Y17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
         <v>1.3</v>
       </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['5', '48', '83']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AJ17" t="n">
         <v>2.2</v>
@@ -2707,106 +2707,106 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="n">
         <v>1</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V18" t="n">
         <v>1</v>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.04</v>
-      </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="X18" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['71']</t>
+          <t>['8', '58', '75']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>['11', '23', '32', '55']</t>
         </is>
       </c>
       <c r="AG18" t="n">
         <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.09</v>
+        <v>1.57</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AJ18" t="n">
         <v>2.6</v>
@@ -2836,16 +2836,16 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sigma Olomouc II</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
@@ -2854,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.87</v>
+        <v>3.35</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>3.7</v>
+        <v>2.02</v>
       </c>
       <c r="O19" t="n">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.47</v>
+        <v>2.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="T19" t="n">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="U19" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="V19" t="n">
         <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X19" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="Z19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.9</v>
       </c>
-      <c r="AA19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['54', '72']</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="AG19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.22</v>
       </c>
-      <c r="AH19" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AI19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>2.38</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45763.5</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,16 +2965,16 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>2.6</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['66']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45763.5</v>
@@ -3094,109 +3094,109 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Varnsdorf</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="J21" t="n">
-        <v>3</v>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.65</v>
+        <v>2.79</v>
       </c>
       <c r="P21" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="U21" t="n">
         <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X21" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD21" t="n">
         <v>2</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['8', '58', '75']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['11', '23', '32', '55']</t>
+          <t>['16', '52']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45763.5</v>
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>1</v>
       </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.35</v>
+        <v>2.58</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N22" t="n">
-        <v>2.02</v>
+        <v>2.75</v>
       </c>
       <c r="O22" t="n">
-        <v>4.33</v>
+        <v>3.15</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.35</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X22" t="n">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AD22" t="n">
         <v>1.9</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['5', '48', '83']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45763.5</v>
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Varnsdorf</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Sigma Olomouc II</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
         <v>1</v>
       </c>
-      <c r="H23" t="n">
-        <v>2</v>
-      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,22 +3378,22 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P23" t="n">
         <v>2.2</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.02</v>
-      </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>4.47</v>
       </c>
       <c r="R23" t="n">
         <v>1.36</v>
@@ -3402,59 +3402,59 @@
         <v>2.9</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA23" t="n">
         <v>3.2</v>
       </c>
-      <c r="Y23" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.28</v>
-      </c>
       <c r="AB23" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['54', '72']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['16', '52']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45763.5</v>
@@ -3729,35 +3729,35 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.65</v>
+        <v>14</v>
       </c>
       <c r="M26" t="n">
-        <v>3.95</v>
+        <v>8.6</v>
       </c>
       <c r="N26" t="n">
-        <v>6.8</v>
+        <v>1.14</v>
       </c>
       <c r="O26" t="n">
-        <v>2.1</v>
+        <v>15</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.3</v>
+        <v>1.44</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="Z26" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>['43', '48']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['16', '26', '45', '61', '81']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.36</v>
+        <v>6.5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.4</v>
+        <v>1.11</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45763.54166666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,19 +3868,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>1.65</v>
+        <v>3.7</v>
       </c>
       <c r="O27" t="n">
-        <v>4.75</v>
+        <v>2.54</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.3</v>
+        <v>4.55</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['45+6', '69', '89']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['28', '49']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
       <c r="AI27" t="n">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45763.54166666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.9</v>
+        <v>2.52</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7</v>
+        <v>2.66</v>
       </c>
       <c r="O28" t="n">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
         <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.55</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['45+6', '69', '89']</t>
+          <t>['12', '14', '18', '22', '61', '74']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45763.54166666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>14</v>
+        <v>1.99</v>
       </c>
       <c r="M29" t="n">
-        <v>8.6</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>1.14</v>
+        <v>3.2</v>
       </c>
       <c r="O29" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.88</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.44</v>
+        <v>4.15</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.38</v>
+        <v>3.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['43', '48']</t>
+          <t>['20', '51']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['16', '26', '45', '61', '81']</t>
+          <t>['61', '87']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI29" t="n">
-        <v>6.5</v>
+        <v>1.67</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.11</v>
+        <v>2.4</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45763.54166666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,19 +4255,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.99</v>
+        <v>4.1</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>3.2</v>
+        <v>1.65</v>
       </c>
       <c r="O30" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="P30" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.15</v>
+        <v>2.3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>1.85</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['20', '51']</t>
+          <t>['28', '49']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['61', '87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45763.54166666666</v>
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,22 +4539,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.52</v>
+        <v>14</v>
       </c>
       <c r="M32" t="n">
-        <v>3.36</v>
+        <v>3.77</v>
       </c>
       <c r="N32" t="n">
-        <v>2.66</v>
+        <v>1.37</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="P32" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4597,12 +4597,12 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['12', '14', '18', '22', '61', '74']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '38', '66', '90']</t>
         </is>
       </c>
       <c r="AG32" t="n">
@@ -4612,10 +4612,10 @@
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.83</v>
+        <v>4.33</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.05</v>
+        <v>1.25</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45763.54166666666</v>
@@ -4632,119 +4632,119 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z33" t="n">
         <v>2</v>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>14</v>
-      </c>
-      <c r="M33" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="O33" t="n">
-        <v>7</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AA33" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>['27', '38', '66', '90']</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI33" t="n">
-        <v>4.33</v>
+        <v>1.36</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.25</v>
+        <v>3.4</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45763.54166666666</v>
@@ -5932,16 +5932,16 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
         <v>2</v>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.68</v>
+        <v>2.7</v>
       </c>
       <c r="M43" t="n">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="N43" t="n">
-        <v>4.6</v>
+        <v>2.52</v>
       </c>
       <c r="O43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X43" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD43" t="n">
         <v>2.2</v>
       </c>
-      <c r="P43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X43" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['58', '61']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['65', '90+3']</t>
+          <t>['52', '76']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.2</v>
+        <v>1.49</v>
       </c>
       <c r="AH43" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ43" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>2.88</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45763.66666666666</v>
@@ -6061,16 +6061,16 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
         <v>2</v>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.7</v>
+        <v>1.68</v>
       </c>
       <c r="M44" t="n">
-        <v>3.74</v>
+        <v>4.5</v>
       </c>
       <c r="N44" t="n">
-        <v>2.52</v>
+        <v>4.6</v>
       </c>
       <c r="O44" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="P44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T44" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q44" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U44" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X44" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>['67']</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>['65', '90+3']</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI44" t="n">
         <v>1.44</v>
       </c>
-      <c r="V44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X44" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>['58', '61']</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>['52', '76']</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ44" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45763.66666666666</v>
@@ -6706,19 +6706,19 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N49" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="O49" t="n">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="P49" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="R49" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="S49" t="n">
         <v>2.4</v>
       </c>
       <c r="T49" t="n">
-        <v>3.3</v>
+        <v>3.77</v>
       </c>
       <c r="U49" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V49" t="n">
         <v>1.1</v>
       </c>
       <c r="W49" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="X49" t="n">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.45</v>
+        <v>2.71</v>
       </c>
       <c r="Z49" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>['63', '82']</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI49" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA49" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>['64']</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ49" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45763.8125</v>
@@ -6835,19 +6835,19 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="M50" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="O50" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="P50" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q50" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="R50" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="S50" t="n">
         <v>2.4</v>
       </c>
       <c r="T50" t="n">
-        <v>3.77</v>
+        <v>3.3</v>
       </c>
       <c r="U50" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V50" t="n">
         <v>1.1</v>
       </c>
       <c r="W50" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="X50" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="Z50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH50" t="n">
         <v>1.46</v>
       </c>
-      <c r="AA50" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>['63', '82']</t>
-        </is>
-      </c>
-      <c r="AG50" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AI50" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AJ50" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45763.8125</v>
@@ -6964,25 +6964,25 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O51" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P51" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X51" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y51" t="n">
         <v>2.1</v>
       </c>
-      <c r="M51" t="n">
+      <c r="Z51" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>['26', '35']</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AJ51" t="n">
         <v>2.75</v>
-      </c>
-      <c r="N51" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O51" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P51" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T51" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X51" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>['42']</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>2.64</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45763.83333333334</v>
@@ -7093,25 +7093,25 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -7119,83 +7119,83 @@
         </is>
       </c>
       <c r="L52" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M52" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O52" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X52" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>['42']</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI52" t="n">
         <v>1.73</v>
       </c>
-      <c r="M52" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N52" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O52" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S52" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T52" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X52" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>['26', '35']</t>
-        </is>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AJ52" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45763.83333333334</v>
@@ -7609,22 +7609,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -7635,83 +7635,83 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="M56" t="n">
-        <v>6.5</v>
+        <v>3.05</v>
       </c>
       <c r="N56" t="n">
-        <v>13.93</v>
+        <v>3.1</v>
       </c>
       <c r="O56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P56" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>4</v>
+      </c>
+      <c r="R56" t="n">
         <v>1.57</v>
       </c>
-      <c r="P56" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.26</v>
-      </c>
       <c r="S56" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="T56" t="n">
-        <v>2.3</v>
+        <v>3.63</v>
       </c>
       <c r="U56" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="V56" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="W56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB56" t="n">
         <v>1.15</v>
       </c>
-      <c r="X56" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AC56" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>['13', '18', '22', '56', '71', '81']</t>
+          <t>['37', '74']</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AH56" t="n">
-        <v>4.4</v>
+        <v>1.55</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.22</v>
+        <v>2.1</v>
       </c>
       <c r="AJ56" t="n">
-        <v>4.75</v>
+        <v>2</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45763.89583333334</v>
@@ -7738,22 +7738,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -7764,83 +7764,83 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="M57" t="n">
-        <v>3.05</v>
+        <v>6.5</v>
       </c>
       <c r="N57" t="n">
-        <v>3.1</v>
+        <v>13.93</v>
       </c>
       <c r="O57" t="n">
-        <v>3.2</v>
+        <v>1.57</v>
       </c>
       <c r="P57" t="n">
-        <v>2.02</v>
+        <v>2.75</v>
       </c>
       <c r="Q57" t="n">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="R57" t="n">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="S57" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X57" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z57" t="n">
         <v>2.25</v>
       </c>
-      <c r="T57" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X57" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AA57" t="n">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>['37', '74']</t>
+          <t>['13', '18', '22', '56', '71', '81']</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.55</v>
+        <v>4.4</v>
       </c>
       <c r="AI57" t="n">
-        <v>2.1</v>
+        <v>1.22</v>
       </c>
       <c r="AJ57" t="n">
-        <v>2</v>
+        <v>4.75</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45763.89583333334</v>
